--- a/event_supervisors_report.xlsx
+++ b/event_supervisors_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb4a1c0c7a4389a8/Documents/GitHub/GoLive_Staffing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_326960F20553C8813FF273E9AD6B3B89787B51BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56D21B10-A2FD-4C54-9111-4CB40EA5DC20}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_326960F20553C8813FF273E9AD6B3B89787B51BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD0A2745-EFF3-4E22-BF45-594337550FF9}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$87</definedName>
   </definedNames>
   <calcPr calcId="124519" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="518">
   <si>
     <t>Employee ID</t>
   </si>
@@ -64,9 +64,6 @@
     <t>David Marroquin Cordero</t>
   </si>
   <si>
-    <t>James Colson</t>
-  </si>
-  <si>
     <t>Oscar Apodaca</t>
   </si>
   <si>
@@ -88,9 +85,6 @@
     <t>Carmen Madani</t>
   </si>
   <si>
-    <t>Jeanne Reeser</t>
-  </si>
-  <si>
     <t>Ric St. John</t>
   </si>
   <si>
@@ -100,24 +94,9 @@
     <t>Carlos Basurto</t>
   </si>
   <si>
-    <t>Toribio Torres</t>
-  </si>
-  <si>
     <t>Cecilia Marquez</t>
   </si>
   <si>
-    <t>Daniela Raynes</t>
-  </si>
-  <si>
-    <t>Deontay Epps</t>
-  </si>
-  <si>
-    <t>William Bunn</t>
-  </si>
-  <si>
-    <t>Carlos Reyes</t>
-  </si>
-  <si>
     <t>Christopher Terry</t>
   </si>
   <si>
@@ -133,15 +112,9 @@
     <t>Jong Lu</t>
   </si>
   <si>
-    <t>Leroy Ortega</t>
-  </si>
-  <si>
     <t>Mark Perrigo</t>
   </si>
   <si>
-    <t>Kimberly Westbrook</t>
-  </si>
-  <si>
     <t>Terry Scott-Mitchell</t>
   </si>
   <si>
@@ -154,18 +127,6 @@
     <t>Robert Rubalcaba</t>
   </si>
   <si>
-    <t>Victor Gutierrez</t>
-  </si>
-  <si>
-    <t>Amera Mathews</t>
-  </si>
-  <si>
-    <t>Molly Dinneen</t>
-  </si>
-  <si>
-    <t>Vanessa Dorman (Mitchell)</t>
-  </si>
-  <si>
     <t>Xavier Miller</t>
   </si>
   <si>
@@ -178,27 +139,15 @@
     <t>Hans Hernke</t>
   </si>
   <si>
-    <t>Terence Duke</t>
-  </si>
-  <si>
     <t>Shey Garland</t>
   </si>
   <si>
-    <t>Maria Zuniga</t>
-  </si>
-  <si>
-    <t>Maria Brockett</t>
-  </si>
-  <si>
     <t>Alisha Arnold</t>
   </si>
   <si>
     <t>Leah Zahner</t>
   </si>
   <si>
-    <t>Vandarith Tep</t>
-  </si>
-  <si>
     <t>Erica Fleming</t>
   </si>
   <si>
@@ -208,54 +157,18 @@
     <t>Amberlyn Silva</t>
   </si>
   <si>
-    <t>Charles Roche</t>
-  </si>
-  <si>
-    <t>Jennifer Lobl</t>
-  </si>
-  <si>
-    <t>Ruben Gil</t>
-  </si>
-  <si>
-    <t>Karen Huggett</t>
-  </si>
-  <si>
-    <t>Fred Torres</t>
-  </si>
-  <si>
-    <t>Vanessa Verbeck</t>
-  </si>
-  <si>
-    <t>Samira Zeruk</t>
-  </si>
-  <si>
-    <t>Fouzia Burfield</t>
-  </si>
-  <si>
-    <t>Dan Draper</t>
-  </si>
-  <si>
     <t>Diego Torres</t>
   </si>
   <si>
     <t>Michael Freitag</t>
   </si>
   <si>
-    <t>William Barragan</t>
-  </si>
-  <si>
-    <t>Frank De Alba</t>
-  </si>
-  <si>
     <t>Christopher Hatanelas</t>
   </si>
   <si>
     <t>Elias Welsh</t>
   </si>
   <si>
-    <t>Melanie Sampson</t>
-  </si>
-  <si>
     <t>Jorgelina Mangiaterra Tompkins</t>
   </si>
   <si>
@@ -265,9 +178,6 @@
     <t>Alicia Ruvalcaba</t>
   </si>
   <si>
-    <t>Tiara Mitchell</t>
-  </si>
-  <si>
     <t>Andrew Powitzky</t>
   </si>
   <si>
@@ -310,12 +220,6 @@
     <t>Nancy Shugg</t>
   </si>
   <si>
-    <t>Leigh Pollitt</t>
-  </si>
-  <si>
-    <t>Esther Montoya</t>
-  </si>
-  <si>
     <t>Cesar Munguia</t>
   </si>
   <si>
@@ -325,48 +229,18 @@
     <t>Amber Denman</t>
   </si>
   <si>
-    <t>Evan Spriggs</t>
-  </si>
-  <si>
     <t>Simon Schwarz</t>
   </si>
   <si>
-    <t>Cameron Allen</t>
-  </si>
-  <si>
-    <t>Stephanie Hass</t>
-  </si>
-  <si>
     <t>Natsko Mckissack</t>
   </si>
   <si>
-    <t>Laura Coder</t>
-  </si>
-  <si>
-    <t>Gabriel Uribe</t>
-  </si>
-  <si>
-    <t>Ricardo Pichardo</t>
-  </si>
-  <si>
     <t>Emery Pierce</t>
   </si>
   <si>
-    <t>Alexis Diamond</t>
-  </si>
-  <si>
     <t>Celeste Crowell</t>
   </si>
   <si>
-    <t>Brian Burns</t>
-  </si>
-  <si>
-    <t>Kiana Tanksley</t>
-  </si>
-  <si>
-    <t>Kalei Castillon</t>
-  </si>
-  <si>
     <t>Kathy Nguyen</t>
   </si>
   <si>
@@ -376,12 +250,6 @@
     <t>Madison Stephan</t>
   </si>
   <si>
-    <t>Victoria Franciscous</t>
-  </si>
-  <si>
-    <t>Thrasius Duncan</t>
-  </si>
-  <si>
     <t>Jonah Bornilla</t>
   </si>
   <si>
@@ -391,33 +259,18 @@
     <t>Beth (prefers Shieya) Flotho</t>
   </si>
   <si>
-    <t>Martin Heredia Huastes</t>
-  </si>
-  <si>
-    <t>Zachariah Pagela</t>
-  </si>
-  <si>
     <t>Ryan Foltz</t>
   </si>
   <si>
     <t>Shelley Gronewold</t>
   </si>
   <si>
-    <t>Travis Jones</t>
-  </si>
-  <si>
     <t>Diana Gutierrez</t>
   </si>
   <si>
     <t>Meagan Wise</t>
   </si>
   <si>
-    <t>Antonio Huerta</t>
-  </si>
-  <si>
-    <t>Brett King</t>
-  </si>
-  <si>
     <t>Salama Graham</t>
   </si>
   <si>
@@ -427,54 +280,27 @@
     <t>Rosa Madriz</t>
   </si>
   <si>
-    <t>Sarah Cooper</t>
-  </si>
-  <si>
-    <t>Jasmine Abad</t>
-  </si>
-  <si>
     <t>Tara Barnett</t>
   </si>
   <si>
-    <t>Stephanie Rodriguez gomez</t>
-  </si>
-  <si>
     <t>Khalila Salahuddin</t>
   </si>
   <si>
     <t>Jacqueline Ramsey-Jordan</t>
   </si>
   <si>
-    <t>Nan Luh</t>
-  </si>
-  <si>
-    <t>Omari Khalfani</t>
-  </si>
-  <si>
-    <t>Drew Mergens</t>
-  </si>
-  <si>
-    <t>Schae Beaudoin</t>
-  </si>
-  <si>
     <t>Djuan Summerville</t>
   </si>
   <si>
     <t>John Brenning</t>
   </si>
   <si>
-    <t>Christine Ritchotte</t>
-  </si>
-  <si>
     <t>Myisha Smith</t>
   </si>
   <si>
     <t>Alberto Ayala</t>
   </si>
   <si>
-    <t>Rischelle Urban</t>
-  </si>
-  <si>
     <t>Jennifer Vigneault</t>
   </si>
   <si>
@@ -496,9 +322,6 @@
     <t>marroquind1986@gmail.com</t>
   </si>
   <si>
-    <t>jamesfostercolson@gmail.com</t>
-  </si>
-  <si>
     <t>oapodaca7@gmail.com</t>
   </si>
   <si>
@@ -520,9 +343,6 @@
     <t>carmenrenderos@me.com</t>
   </si>
   <si>
-    <t>reeserjeanne@gmail.com</t>
-  </si>
-  <si>
     <t>rsj808@gmail.com</t>
   </si>
   <si>
@@ -532,24 +352,9 @@
     <t>basurtocarlos@icloud.com</t>
   </si>
   <si>
-    <t>toribiotorres@ymail.com</t>
-  </si>
-  <si>
     <t>lusve@hotmail.com</t>
   </si>
   <si>
-    <t>danielalouise74@gmail.com</t>
-  </si>
-  <si>
-    <t>Deontaybrand@gmail.com</t>
-  </si>
-  <si>
-    <t>Wbunn3@yahoo.com</t>
-  </si>
-  <si>
-    <t>cr69hospitality@gmail.com</t>
-  </si>
-  <si>
     <t>cterry2011@gmail.com</t>
   </si>
   <si>
@@ -565,15 +370,9 @@
     <t>jmoonlu@gmail.com</t>
   </si>
   <si>
-    <t>ortegaleroy@yahoo.com</t>
-  </si>
-  <si>
     <t>markperrigo8@gmail.com</t>
   </si>
   <si>
-    <t>kimwestbrook2006@gmail.com</t>
-  </si>
-  <si>
     <t>tesatg57@gmail.com</t>
   </si>
   <si>
@@ -586,18 +385,6 @@
     <t>robertmhs@protonmail.com</t>
   </si>
   <si>
-    <t>chefvictorg@yahoo.com</t>
-  </si>
-  <si>
-    <t>a.amathews@yahoo.com</t>
-  </si>
-  <si>
-    <t>msdinneen.92@gmail.com</t>
-  </si>
-  <si>
-    <t>snap-dragon23@sudomail.com</t>
-  </si>
-  <si>
     <t>millertime09@me.com</t>
   </si>
   <si>
@@ -610,27 +397,15 @@
     <t>actorhans223@aol.com</t>
   </si>
   <si>
-    <t>terencekirkduke@gmail.com</t>
-  </si>
-  <si>
     <t>shey.garland@gmail.com</t>
   </si>
   <si>
-    <t>kyutpnay007@gmail.com</t>
-  </si>
-  <si>
-    <t>daltonmarisa1@gmail.com</t>
-  </si>
-  <si>
     <t>alisha.arnold12@gmail.com</t>
   </si>
   <si>
     <t>leahzahner888@gmail.com</t>
   </si>
   <si>
-    <t>Vdarith117@gmail.com</t>
-  </si>
-  <si>
     <t>e_fleming@live.com</t>
   </si>
   <si>
@@ -640,54 +415,18 @@
     <t>amberlynsilva@yahoo.com</t>
   </si>
   <si>
-    <t>tyler9roche@gmail.com</t>
-  </si>
-  <si>
-    <t>lobljennifer97@gmail.com</t>
-  </si>
-  <si>
-    <t>lignebur72@yahoo.com</t>
-  </si>
-  <si>
-    <t>21huggettky@gmail.com</t>
-  </si>
-  <si>
-    <t>FT.Management.LA@gmail.com</t>
-  </si>
-  <si>
-    <t>Vverbeck778@gmail.com</t>
-  </si>
-  <si>
-    <t>samzeruk77@gmail.com</t>
-  </si>
-  <si>
-    <t>fouziad@gmail.com</t>
-  </si>
-  <si>
-    <t>lvbratboy@hotmail.com</t>
-  </si>
-  <si>
     <t>marzam7@gmail.com</t>
   </si>
   <si>
     <t>Mikef730@gmail.com</t>
   </si>
   <si>
-    <t>williambarragan25@yahoo.com</t>
-  </si>
-  <si>
-    <t>Ucdfrank@gmail.com</t>
-  </si>
-  <si>
     <t>Hatanelas@yahoo.com</t>
   </si>
   <si>
     <t>eliaswelsh@yahoo.com</t>
   </si>
   <si>
-    <t>msampsonite@aol.com</t>
-  </si>
-  <si>
     <t>geodora@gmail.com</t>
   </si>
   <si>
@@ -697,9 +436,6 @@
     <t>amoralas@hotmail.com</t>
   </si>
   <si>
-    <t>mitchelltiara222@gmail.com</t>
-  </si>
-  <si>
     <t>brunedianne130@gmail.com</t>
   </si>
   <si>
@@ -742,12 +478,6 @@
     <t>Nancyshugg@msn.com</t>
   </si>
   <si>
-    <t>Leighpollitt@icloud.com</t>
-  </si>
-  <si>
-    <t>montoya198252@gmail.com</t>
-  </si>
-  <si>
     <t>Ceemj45@gmail.com</t>
   </si>
   <si>
@@ -757,48 +487,18 @@
     <t>andreamber7879@yahoo.com</t>
   </si>
   <si>
-    <t>Evan.michael.spriggs@gmail.com</t>
-  </si>
-  <si>
     <t>simon@no-nameproductions.com</t>
   </si>
   <si>
-    <t>Cameronrangel668@gmail.com</t>
-  </si>
-  <si>
-    <t>Steffani.symons@gmail.com</t>
-  </si>
-  <si>
     <t>natskos@yahoo.com</t>
   </si>
   <si>
-    <t>fisher365222@gmail.com</t>
-  </si>
-  <si>
-    <t>gabeuribe08@gmail.com</t>
-  </si>
-  <si>
-    <t>RicardopichardoLA@gmail.com</t>
-  </si>
-  <si>
     <t>emerypierce@gmail.com</t>
   </si>
   <si>
-    <t>alexisdiamond19@gmail.com</t>
-  </si>
-  <si>
     <t>cottamcc@yahoo.com</t>
   </si>
   <si>
-    <t>stpatrick480@gmail.com</t>
-  </si>
-  <si>
-    <t>kiana.tanksley@gmail.com</t>
-  </si>
-  <si>
-    <t>Kbnjc2010@gmail.com</t>
-  </si>
-  <si>
     <t>Opn249@gmail.com</t>
   </si>
   <si>
@@ -808,12 +508,6 @@
     <t>Madi.stephan@yahoo.com</t>
   </si>
   <si>
-    <t>torifranciscous@att.net</t>
-  </si>
-  <si>
-    <t>vicfran2471@gmail.com</t>
-  </si>
-  <si>
     <t>bornillajonah@gmail.com</t>
   </si>
   <si>
@@ -823,33 +517,18 @@
     <t>Chefshieya@gmail.com</t>
   </si>
   <si>
-    <t>Mah82006@yahoo.com</t>
-  </si>
-  <si>
-    <t>Zachaapagelaa@gmail.com</t>
-  </si>
-  <si>
     <t>Socalhospitality@yahoo.com</t>
   </si>
   <si>
     <t>shelley.gronewold@yahoo.com</t>
   </si>
   <si>
-    <t>Tjones75@hotmail.com</t>
-  </si>
-  <si>
     <t>Dianalgutierrez89@gmail.com</t>
   </si>
   <si>
     <t>meaganewise@gmail.com</t>
   </si>
   <si>
-    <t>Tonyoe310@gmail.com</t>
-  </si>
-  <si>
-    <t>Brett.king914@gmail.com</t>
-  </si>
-  <si>
     <t>najima.graham@outlook.com</t>
   </si>
   <si>
@@ -859,54 +538,27 @@
     <t>madrizrosa3@gmail.com</t>
   </si>
   <si>
-    <t>sarah.cooper2014@gmail.com</t>
-  </si>
-  <si>
-    <t>jasabad@icloud.com</t>
-  </si>
-  <si>
     <t>Btara702@gmail.com</t>
   </si>
   <si>
-    <t>Kaymartinez327@gmail.com</t>
-  </si>
-  <si>
     <t>Khalilashani@gmail.com</t>
   </si>
   <si>
     <t>Chefjackie@pangeacateringla.com</t>
   </si>
   <si>
-    <t>njluh0129@gmail.com</t>
-  </si>
-  <si>
-    <t>Omari.najja2@gmail.com</t>
-  </si>
-  <si>
-    <t>Drewjmergens@gmail.com</t>
-  </si>
-  <si>
-    <t>Schaeabeaudoin@gmail.com</t>
-  </si>
-  <si>
     <t>Djuansummerville2@icloud.com</t>
   </si>
   <si>
     <t>Chefjohnpaul321@gmail.com</t>
   </si>
   <si>
-    <t>Christineritchotte@gmail.com</t>
-  </si>
-  <si>
     <t>Myishasmith517@gmail.com</t>
   </si>
   <si>
     <t>Albertoayala91210@gmail.com</t>
   </si>
   <si>
-    <t>Rischelle.urban@gmail.com</t>
-  </si>
-  <si>
     <t>Jenniferlvigneault@gmail.com</t>
   </si>
   <si>
@@ -928,9 +580,6 @@
     <t>818-669-8081</t>
   </si>
   <si>
-    <t>310-694-6367</t>
-  </si>
-  <si>
     <t>213-458-6985</t>
   </si>
   <si>
@@ -952,9 +601,6 @@
     <t>000-000-0000</t>
   </si>
   <si>
-    <t>949-842-8155</t>
-  </si>
-  <si>
     <t>310-801-0930</t>
   </si>
   <si>
@@ -964,24 +610,9 @@
     <t>213-318-9963</t>
   </si>
   <si>
-    <t>818-723-1866</t>
-  </si>
-  <si>
     <t>714-420-3453</t>
   </si>
   <si>
-    <t>424-332-8532</t>
-  </si>
-  <si>
-    <t>347) 551-5374</t>
-  </si>
-  <si>
-    <t>951-390-6709</t>
-  </si>
-  <si>
-    <t>818-669-7825</t>
-  </si>
-  <si>
     <t>310-936-1387</t>
   </si>
   <si>
@@ -997,15 +628,9 @@
     <t>310-220-1038</t>
   </si>
   <si>
-    <t>818-605-0641</t>
-  </si>
-  <si>
     <t>442-342-4400</t>
   </si>
   <si>
-    <t>512-565-8582</t>
-  </si>
-  <si>
     <t>323-829-4817</t>
   </si>
   <si>
@@ -1018,18 +643,6 @@
     <t>213-570-5675</t>
   </si>
   <si>
-    <t>626-848-4697</t>
-  </si>
-  <si>
-    <t>310-621-4734</t>
-  </si>
-  <si>
-    <t>714-476-0042</t>
-  </si>
-  <si>
-    <t>323-703-9080</t>
-  </si>
-  <si>
     <t>214-232-7917</t>
   </si>
   <si>
@@ -1042,27 +655,15 @@
     <t>818-468-9693</t>
   </si>
   <si>
-    <t>310-406-6341</t>
-  </si>
-  <si>
     <t>630-386-1408</t>
   </si>
   <si>
-    <t>323-384-3675</t>
-  </si>
-  <si>
-    <t>408-469-0868</t>
-  </si>
-  <si>
     <t>309-472-9190</t>
   </si>
   <si>
     <t>323-893-8235</t>
   </si>
   <si>
-    <t>949-421-9604</t>
-  </si>
-  <si>
     <t>661-269-3241</t>
   </si>
   <si>
@@ -1072,54 +673,18 @@
     <t>310-606-9378</t>
   </si>
   <si>
-    <t>323-614-9426</t>
-  </si>
-  <si>
-    <t>951-732-6225</t>
-  </si>
-  <si>
-    <t>626-926-9392</t>
-  </si>
-  <si>
-    <t>626-922-1537</t>
-  </si>
-  <si>
-    <t>323-810-1379</t>
-  </si>
-  <si>
-    <t>702-827-6651</t>
-  </si>
-  <si>
-    <t>646-807-7245</t>
-  </si>
-  <si>
-    <t>917-660-3534</t>
-  </si>
-  <si>
-    <t>725-287-4079</t>
-  </si>
-  <si>
     <t>323-892-6508</t>
   </si>
   <si>
     <t>516-477-7965</t>
   </si>
   <si>
-    <t>925-339-9649</t>
-  </si>
-  <si>
-    <t>661-470-1443</t>
-  </si>
-  <si>
     <t>310-270-7870</t>
   </si>
   <si>
     <t>510-847-7453</t>
   </si>
   <si>
-    <t>310-561-4212</t>
-  </si>
-  <si>
     <t>562-589-2442</t>
   </si>
   <si>
@@ -1129,9 +694,6 @@
     <t>909-219-0772</t>
   </si>
   <si>
-    <t>323-216-8866</t>
-  </si>
-  <si>
     <t>424-291-0384</t>
   </si>
   <si>
@@ -1174,12 +736,6 @@
     <t>949-702-1160</t>
   </si>
   <si>
-    <t>310-773-6231</t>
-  </si>
-  <si>
-    <t>442-454-5093</t>
-  </si>
-  <si>
     <t>323-542-1939</t>
   </si>
   <si>
@@ -1189,48 +745,18 @@
     <t>442-260-4279</t>
   </si>
   <si>
-    <t>840-245-1807</t>
-  </si>
-  <si>
     <t>212-920-7880</t>
   </si>
   <si>
-    <t>760-485-3026</t>
-  </si>
-  <si>
-    <t>442-999-1310</t>
-  </si>
-  <si>
     <t>310-694-7204</t>
   </si>
   <si>
-    <t>203-910-3085</t>
-  </si>
-  <si>
-    <t>619-577-9822</t>
-  </si>
-  <si>
-    <t>213-791-6357</t>
-  </si>
-  <si>
     <t>810-936-1847</t>
   </si>
   <si>
-    <t>702-588-3732</t>
-  </si>
-  <si>
     <t>435-691-2437</t>
   </si>
   <si>
-    <t>480-547-4098</t>
-  </si>
-  <si>
-    <t>256-617-1480</t>
-  </si>
-  <si>
-    <t>619-804-1515</t>
-  </si>
-  <si>
     <t>657-758-3882</t>
   </si>
   <si>
@@ -1240,12 +766,6 @@
     <t>951-567-1134</t>
   </si>
   <si>
-    <t>315-237-0777</t>
-  </si>
-  <si>
-    <t>213-294-1108</t>
-  </si>
-  <si>
     <t>702-738-5107</t>
   </si>
   <si>
@@ -1255,33 +775,18 @@
     <t>917-325-2294</t>
   </si>
   <si>
-    <t>213-658-8194</t>
-  </si>
-  <si>
-    <t>559-744-2070</t>
-  </si>
-  <si>
     <t>949-558-7790</t>
   </si>
   <si>
     <t>702-672-2231</t>
   </si>
   <si>
-    <t>805-674-9113</t>
-  </si>
-  <si>
     <t>760-550-2830</t>
   </si>
   <si>
     <t>951-323-7415</t>
   </si>
   <si>
-    <t>702-812-9323</t>
-  </si>
-  <si>
-    <t>702-400-6640</t>
-  </si>
-  <si>
     <t>615-602-4195</t>
   </si>
   <si>
@@ -1291,54 +796,27 @@
     <t>707-774-1115</t>
   </si>
   <si>
-    <t>870-819-6783</t>
-  </si>
-  <si>
-    <t>725-267-7738</t>
-  </si>
-  <si>
     <t>702-592-9542</t>
   </si>
   <si>
-    <t>702-357-7479</t>
-  </si>
-  <si>
     <t>626-750-9912</t>
   </si>
   <si>
     <t>541-221-1028</t>
   </si>
   <si>
-    <t>949-331-4899</t>
-  </si>
-  <si>
-    <t>909-642-4106</t>
-  </si>
-  <si>
-    <t>612-227-6616</t>
-  </si>
-  <si>
-    <t>860-977-2477</t>
-  </si>
-  <si>
     <t>310-993-8846</t>
   </si>
   <si>
     <t>714-326-3420</t>
   </si>
   <si>
-    <t>949-290-5281</t>
-  </si>
-  <si>
     <t>661-521-9237</t>
   </si>
   <si>
     <t>510-318-4014</t>
   </si>
   <si>
-    <t>951-973-9424</t>
-  </si>
-  <si>
     <t>617-580-6190</t>
   </si>
   <si>
@@ -1360,9 +838,6 @@
     <t>Manager, Sous Chef, Assistant Chef</t>
   </si>
   <si>
-    <t>Senior Executive Chef &amp; General Manager, Executive Chef, Food &amp; Beverage Director, Executive Sous Chef, Executive Chef &amp; General Manager</t>
-  </si>
-  <si>
     <t>Assistant/General Manager</t>
   </si>
   <si>
@@ -1384,9 +859,6 @@
     <t>Chef supervisor</t>
   </si>
   <si>
-    <t>General Manager, Assistant Manager</t>
-  </si>
-  <si>
     <t>Captain, Catering Manager, Event Planning</t>
   </si>
   <si>
@@ -1399,18 +871,6 @@
     <t>Suite Supervisor</t>
   </si>
   <si>
-    <t>Manager, Catering Manager</t>
-  </si>
-  <si>
-    <t>Shift Supervisor, Barista Lead</t>
-  </si>
-  <si>
-    <t>Banquet Manager</t>
-  </si>
-  <si>
-    <t>General Manager, Senior Manager, AGM</t>
-  </si>
-  <si>
     <t>Captain, Banquet Sous Chef, Culinary Supervisor</t>
   </si>
   <si>
@@ -1426,15 +886,9 @@
     <t>Food Supervisor, Manager</t>
   </si>
   <si>
-    <t>Venue Manager, Event Captain</t>
-  </si>
-  <si>
     <t>Banquet Manager, Owner/Manager / Maitre D'hotel</t>
   </si>
   <si>
-    <t>Restaurant General Manager, Restaurant Supervisor</t>
-  </si>
-  <si>
     <t>Banquette Captain, Event Planner, Event Logistics Manager</t>
   </si>
   <si>
@@ -1447,18 +901,6 @@
     <t>Team Captain, Assistant Team Captain, Assistant Manager</t>
   </si>
   <si>
-    <t>Sous Chef/Catering</t>
-  </si>
-  <si>
-    <t>Catering Manager, Lead Line Cook, Catering Assistant Manager</t>
-  </si>
-  <si>
-    <t>FOH/Coffee Bar Supervisor, Manager</t>
-  </si>
-  <si>
-    <t>Assistant GM, Closing Manager</t>
-  </si>
-  <si>
     <t>Captain, Lead Bartender</t>
   </si>
   <si>
@@ -1468,18 +910,9 @@
     <t>Bar Supervisor, General Manager/Food &amp; Beverage Manager, Commercial Kitchen Manager, Scheduling Manager, Supervisor, Lead Server and Trainer, Caterer/Cook (with management duties)</t>
   </si>
   <si>
-    <t>Onsite Captain</t>
-  </si>
-  <si>
     <t>Catering Supervisor, Banquet Captain, Chef/Lodge Manager, Executive Chef/General Manager, Chef Manager, General Manager</t>
   </si>
   <si>
-    <t>Manager, Lead Barista</t>
-  </si>
-  <si>
-    <t>Catering Manager, Trainer, Apprentice/Restaurant Management</t>
-  </si>
-  <si>
     <t>Lead Private Event Chef, Lead Event People Manager</t>
   </si>
   <si>
@@ -1492,33 +925,6 @@
     <t>Food and Beverage Supervisor, HR Assistant / Floor Supervisor, Financial Coordinator / Events Director</t>
   </si>
   <si>
-    <t>Server Captain</t>
-  </si>
-  <si>
-    <t>Shift Manager, Lead Server</t>
-  </si>
-  <si>
-    <t>Catering Supervisor</t>
-  </si>
-  <si>
-    <t>Manager Supervisor</t>
-  </si>
-  <si>
-    <t>Concessions/Bar Supervisor</t>
-  </si>
-  <si>
-    <t>Catering Supervisor, Concessions Stand Lead</t>
-  </si>
-  <si>
-    <t>Banquet Captain, Restaurant Manager</t>
-  </si>
-  <si>
-    <t>Food and Beverage Supervisor, Assistant General Manager, Maitre D’/ Manager</t>
-  </si>
-  <si>
-    <t>Zone Lead/Bar Manager, Zone Lead/Registration, Brand Ambassador/Team Lead</t>
-  </si>
-  <si>
     <t>Supervisor, Assistant Manager</t>
   </si>
   <si>
@@ -1528,15 +934,9 @@
     <t>Supervisor</t>
   </si>
   <si>
-    <t>BOH Captain</t>
-  </si>
-  <si>
     <t>Manager, Managing Partner, Opening Unit Manager, Owner</t>
   </si>
   <si>
-    <t>Catering Manager</t>
-  </si>
-  <si>
     <t>Chef Manager, Cafe Manager, Cold Larder Sous Chef</t>
   </si>
   <si>
@@ -1546,9 +946,6 @@
     <t>Assistant Manager, Kitchen Supervisor, Chef/Manager/Guest Relations</t>
   </si>
   <si>
-    <t>Banquet Server Captain</t>
-  </si>
-  <si>
     <t>Captain, Manager</t>
   </si>
   <si>
@@ -1585,12 +982,6 @@
     <t>Operations Manager - Destination Services, Planning Manager, Sales Manager</t>
   </si>
   <si>
-    <t>Bar Supervisor, Manager</t>
-  </si>
-  <si>
-    <t>Housekeeping Supervisor</t>
-  </si>
-  <si>
     <t>Banquet server lead, Event lead, Janitor lead</t>
   </si>
   <si>
@@ -1600,90 +991,42 @@
     <t>Food and Beverage Supervisor, Restaurant Supervisor, Restaurant Manager, Banquet Manager, Event Coordinator, Shift Leader, General Manager</t>
   </si>
   <si>
-    <t>Banquet Supervisor</t>
-  </si>
-  <si>
     <t>Director of Catering &amp; F&amp;B</t>
   </si>
   <si>
-    <t>Event Supervisor</t>
-  </si>
-  <si>
-    <t>Restaurant Manager</t>
-  </si>
-  <si>
     <t>Lead server</t>
   </si>
   <si>
-    <t>Bartender/Manager, Shift Management, Supervising experience</t>
-  </si>
-  <si>
-    <t>Assistant Event Lead</t>
-  </si>
-  <si>
-    <t>Floor Manager</t>
-  </si>
-  <si>
     <t>Food Service Supervisor, Lead Bartender</t>
   </si>
   <si>
-    <t>Front of House Supervisor</t>
-  </si>
-  <si>
     <t>House Supervisor, Charge RN, Previous management experience front of house for a busy restaurant</t>
   </si>
   <si>
-    <t>F&amp;B Shift Supervisor</t>
-  </si>
-  <si>
-    <t>Front of House Supervisor, Front of House Key Holder</t>
-  </si>
-  <si>
-    <t>Lead Bartender / Manager, Front-of-House Manager</t>
-  </si>
-  <si>
     <t>Field Manager, Team Lead, Project Manager, Lead, Assistant Project Manager, Production Assistant</t>
   </si>
   <si>
     <t>Catering Lead, Wedding Coordinator</t>
   </si>
   <si>
-    <t>Event Supervisor, Stand Lead</t>
-  </si>
-  <si>
     <t>Floor Captain (Lead Server), General Manager, Assistant General Manager</t>
   </si>
   <si>
     <t>Executive Chef / Owner, Kitchen Manager</t>
   </si>
   <si>
-    <t>Banquet Captain</t>
-  </si>
-  <si>
-    <t>Head Server</t>
-  </si>
-  <si>
     <t>Banquet Captain, Banquet &amp; Event Lead, Director of Beverage Operations</t>
   </si>
   <si>
     <t>Manager, Supervisor, Team Lead</t>
   </si>
   <si>
-    <t>General Manager, Restaurant Manager</t>
-  </si>
-  <si>
     <t>Front of House Manager, General Manager, Assistant General Manager</t>
   </si>
   <si>
     <t>Lead Server, Shift Manager, Lead Hostess</t>
   </si>
   <si>
-    <t>Bar Apprentice (supervisory capacity)</t>
-  </si>
-  <si>
-    <t>Bar Manager</t>
-  </si>
-  <si>
     <t>Banquet Captain, Assistant Banquet Manager, Captain</t>
   </si>
   <si>
@@ -1693,12 +1036,6 @@
     <t>Banquet Captain, Diningroom Supervisor, Restaurant Manager</t>
   </si>
   <si>
-    <t>Show Manager, House Manager</t>
-  </si>
-  <si>
-    <t>Assistant Manager, Supervisor</t>
-  </si>
-  <si>
     <t>Event Coordinator, Lead Server</t>
   </si>
   <si>
@@ -1708,12 +1045,6 @@
     <t>Catering Manager, Restaurant Manager, Event Coordinator</t>
   </si>
   <si>
-    <t>Shift Supervisor, Assistant General Manager, Barista Shift Supervisor</t>
-  </si>
-  <si>
-    <t>Team Lead</t>
-  </si>
-  <si>
     <t>Restaurant Manager, Owner / Head Chef / Restaurant Manager</t>
   </si>
   <si>
@@ -1747,9 +1078,6 @@
     <t>The candidate held a Manager role at HoneyDew Café where they supervised employees, scheduled shifts, and oversaw daily operations, which is a leadership role in a hospitality setting. Additionally, as a Sous Chef at The Village Bakery &amp; Café, they supervised kitchen food preparation, managed team productivity, and assisted with hiring and training staff, demonstrating supervisory and leadership experience relevant to event or banquet management. Although the roles are primarily culinary, the supervisory and management responsibilities qualify as leadership roles in hospitality.</t>
   </si>
   <si>
-    <t>The candidate has held multiple senior leadership roles in hospitality including Senior Executive Chef &amp; General Manager, Executive Chef, Food &amp; Beverage Director, and Executive Sous Chef. These roles involved managing kitchen and catering operations, overseeing staff, budgeting, event catering, and coordinating with front-of-house teams to ensure seamless dining and event experiences. The candidate has direct experience managing and leading teams in event and catering settings, which qualifies as equivalent to Event Supervisor, Banquet Captain, Catering Manager, or Front of House Manager roles.</t>
-  </si>
-  <si>
     <t>The candidate held leadership roles as Assistant Manager and then General Manager at Le Pain Quotidien for over 12 years, managing a high-volume restaurant with catering sales growth. These roles involved supervising staff, managing operations, increasing catering sales, and ensuring health standards, which qualifies as relevant supervisory experience in a hospitality setting.</t>
   </si>
   <si>
@@ -1771,9 +1099,6 @@
     <t>The candidate held a 'Chef supervisor' role at Green Truck from Nov 2015 to 2018, where they supervised food production and delivery, managed client satisfaction, set tables, arranged decorations, and communicated with team and clients. This role involved leadership and supervisory responsibilities in an event/catering context, which qualifies as equivalent to an Event Supervisor or Banquet Captain.</t>
   </si>
   <si>
-    <t>The candidate held the role of General Manager at The Sandwich Bar (2014-2015) where they coordinated daily management operations, organized and supervised shifts, and ensured compliance with regulations. Additionally, as Assistant Manager at Irvine Village Market (2013-2015), they supervised shifts, organized events, trained employees, and managed daily cash flow. These roles demonstrate leadership and supervisory experience in a hospitality/restaurant setting, qualifying as equivalent to Event Supervisor, Banquet Captain, or Front of House Manager.</t>
-  </si>
-  <si>
     <t>The candidate explicitly lists experience as a 'Captain' and in 'Catering/Event Planning' from 2000 to 2016, indicating leadership roles in event settings. They also mention owning and operating cafes, restaurants, and catering companies, which implies supervisory and management experience. Although much of the recent experience is bartending, the leadership roles and catering management experience qualify them as having held supervisory roles in hospitality/events.</t>
   </si>
   <si>
@@ -1783,24 +1108,9 @@
     <t>The candidate has held supervisory and leadership roles in food service settings, notably as 'Head Food Service' at LA County Sheriff's Department for about 16 years, where they supervised food service workers, managed schedules, and assisted with administrative and quality assurance tasks. Additionally, they were a 'Food Service Supervisor' at Costco Wholesale for over 4 years and promoted to 'Service Supervisor' at Macy's. These roles demonstrate active management and supervisory experience in hospitality-related environments.</t>
   </si>
   <si>
-    <t>The candidate has held the title 'Captain' at TRESLA, which is a recognized supervisory/leadership role in a hospitality setting. The duties include setting up tables and server stations, organizing scullery, and closing duties, indicating responsibility beyond standard server or bartender roles. Although the exact length of time in this role is not specified, it is current and implies at least some supervisory experience.</t>
-  </si>
-  <si>
     <t>The candidate held a Suite Supervisor role at OVG Acrisure Arena from October 2022 to February 2026, where they recruited, trained, and scheduled staff, conducted pre-shift meetings, mentored and motivated staff, managed food and beverage operations, ensured compliance with safety regulations, and handled administrative tasks. This role clearly demonstrates leadership and supervisory responsibilities in an event/hospitality setting.</t>
   </si>
   <si>
-    <t>The candidate held a Manager role at Ottavios Restaurant (1999-2001) where she oversaw hiring, firing, scheduling, assigned table sections, ensured side work completion, handled payments, and secured the premises. Additionally, she was a Catering Manager at Utah Valley University (2001-2002), responsible for training, scheduling, managing wait staff, coordinating between kitchen and dining room, setting up and serving catered events, and ensuring proper execution of events. These roles demonstrate explicit supervisory and leadership experience in hospitality event settings.</t>
-  </si>
-  <si>
-    <t>The candidate has explicit supervisory experience as a 'Shift Supervisor' at Starbucks from 04/2019 to 08/2021, where they delegated tasks, handled cash management, managed inventory, organized opening and closing duties, and coached team members. Additionally, the current role as 'Barista Lead' since 10/2023 indicates leadership responsibilities. These roles demonstrate active management and supervision in a hospitality setting, qualifying the candidate for event or hospitality supervisory roles.</t>
-  </si>
-  <si>
-    <t>The candidate explicitly held the role of Banquet Manager at US OPEN AMERIVENTS from March 2010 to June 2012, where they managed banquet staff during event setup and breakdown, assigned duties, managed bar setup, and interfaced with clients. This clearly demonstrates leadership and supervisory experience in an event/banquet setting.</t>
-  </si>
-  <si>
-    <t>The candidate has held multiple leadership roles such as General Manager, Senior Manager, and AGM in hospitality settings. These roles involved managing events, overseeing front of house and back of house operations, scheduling, training, supervising staff, and coordinating event logistics. Specifically, as General Manager at Monaco Encino, they managed all areas of events from pre-planning through post-event activities, which clearly qualifies as event supervisory experience.</t>
-  </si>
-  <si>
     <t>The candidate has explicit supervisory and leadership experience in hospitality events settings. They have worked as a 'Culinary Specialist' captaining dining halls and catering special events since January 2023, and as a 'Banquet Sous Chef' managing and captaining banquets from May 2014 to December 2019. Additionally, they held a 'Culinary Supervisor' role responsible for coordination and quality control in a hospital cafeteria from February 2011 to March 2012. These roles demonstrate active management and supervision of event teams, qualifying them for leadership roles such as Event Supervisor, Banquet Captain, or Catering Manager.</t>
   </si>
   <si>
@@ -1816,15 +1126,9 @@
     <t>The candidate has explicit supervisory and managerial experience in hospitality settings. As a Food Supervisor at Sodexo (Aug 2025 - Present), they oversee day-to-day operations of catering events, plan and execute special events, and ensure workplace safety. Additionally, as a Manager/Cook at Cosmic Cafe (2000-2005), they managed day-to-day restaurant operations, supervised staff, and handled scheduling and training. These roles demonstrate leadership and supervisory responsibilities in event and food service environments.</t>
   </si>
   <si>
-    <t>The candidate has explicit supervisory and leadership experience in hospitality event settings. As a Venue Manager (02/2019-Present), they managed events with 10-500+ guests, led an event staff of 20+, handled scheduling, training, and payroll. Additionally, as an Event Captain at Compass Group - Levy Concessions (11/2018-Present), they reviewed Banquet Event Orders (BEOs) with event staff and coordinated event execution at major venues. These roles clearly demonstrate event leadership and supervisory responsibilities.</t>
-  </si>
-  <si>
     <t>The candidate explicitly held the role of Banquet Manager at Sodexo / Detroit Institute of Arts from February 2015 to January 2016, managing banquet events with up to 2,000 people, which is a clear supervisory leadership role in an events setting. Additionally, the candidate was Owner/Manager / Maitre D'hotel at two French bistros from 1997 to 2004, roles that involved managing restaurant operations and staff, which also qualifies as leadership experience in hospitality.</t>
   </si>
   <si>
-    <t>The candidate has held multiple supervisory and management roles in restaurant settings, including Restaurant Supervisor and Restaurant General Manager. These roles involved managing staff, scheduling, labor management, counseling and disciplining employees, and ensuring service standards, which clearly demonstrate leadership and supervisory experience in a hospitality environment. The experience spans from 07/2010 to present, totaling approximately 8.5 years.</t>
-  </si>
-  <si>
     <t>The candidate explicitly lists experience as a 'Banquette Captain' which is a recognized supervisory role in banquet/event settings. Additionally, they have managed all aspects of special events, including logistics and catering, vendor management, and event planning from 2006 to 2016, indicating leadership and supervisory responsibilities in event management. This combined experience qualifies them for leadership roles in hospitality event supervision.</t>
   </si>
   <si>
@@ -1837,18 +1141,6 @@
     <t>The candidate has held multiple leadership roles such as Team Captain and Assistant Team Captain at various catering companies from 2017 to present, which involves supervising and leading event teams. Additionally, they held an Assistant Manager role from 1996 to 2016 in a hospitality setting. These roles demonstrate relevant supervisory and leadership experience in event and catering environments.</t>
   </si>
   <si>
-    <t>The candidate held a Sous Chef/Catering role at La Costa Mission from 02/14 to 09/16 where they were responsible for making weekly schedules, supervising stations, ensuring associates clocked in/out, training line cooks, and managing inventory. They also catered private events including weddings and a private beach club, indicating leadership and supervisory responsibilities in a catering/event setting.</t>
-  </si>
-  <si>
-    <t>The candidate held the role of Catering Manager at Sofi Stadium from 11/2021 to 06/2022, where they managed, led, delegated, and motivated a team for catering events including games, concerts, and special events. This role explicitly involved supervisory and leadership responsibilities in an event hospitality setting. Additionally, the candidate served as a Catering Assistant Manager at Greenleaf Chopshop from 12/2011 to 01/2014, assisting in planning and coordinating events and managing customer and vendor relationships, which also supports their supervisory experience in catering. The Lead Line Cook roles, while supervisory in kitchen settings, do not specifically qualify as event or banquet leadership but support their leadership experience in hospitality.</t>
-  </si>
-  <si>
-    <t>The candidate has explicit supervisory experience as a FOH/Coffee Bar Supervisor at Compass Group/Bon Appetit Management Company from January 2022 to present, where they managed front of house staff, coordinated catering setup and service, and handled inventory and scheduling. Additionally, they held a Manager role at Crossroads Cafe from 2014 to 2017 with responsibilities including opening/closing the restaurant, ordering supplies, and overseeing operations. These roles demonstrate leadership and supervisory responsibilities in hospitality settings.</t>
-  </si>
-  <si>
-    <t>The candidate held leadership roles such as Assistant GM and Closing Manager in hospitality settings, which involve supervisory and management responsibilities beyond standard server or bartender duties. These roles demonstrate experience in managing teams and operations, qualifying as equivalent leadership roles in hospitality.</t>
-  </si>
-  <si>
     <t>The candidate held the title 'Captain' at Viki Hall Staffing from 04/2015 to 08/2018, which indicates a supervisory or leadership role in an event setting. Additionally, the 'Lead Bartender' role at Universal Studios Hollywood since 07/2021 suggests a leadership position, though primarily focused on bartending. The Captain role explicitly implies event team leadership, qualifying the candidate.</t>
   </si>
   <si>
@@ -1861,27 +1153,15 @@
     <t>The candidate has held the position of 'Captain' at The Party Staff Inc. from May 2012 to present, which is a leadership/supervisory role in banquet and event settings. This role explicitly indicates managing or leading event teams, qualifying them for event supervisory or banquet captain roles.</t>
   </si>
   <si>
-    <t>The candidate held the role of 'Onsite Captain' at InstaWork from 2023 to present, where they managed and motivated a temporary workforce of 20-80 individuals at major event venues. This role explicitly involves leadership and supervision in an event setting, qualifying as an event supervisory position.</t>
-  </si>
-  <si>
     <t>The candidate has explicit leadership and supervisory experience in hospitality and events settings. Notably, as a Catering Supervisor at Guckenheimer at Google (2018-2019), they were solely responsible for all aspects of the catering department including planning and execution of large-scale events and staff scheduling. They also held the role of Banquet Captain at Epicurean Entertainment (2012-2014), managing banquet operations. Additional relevant leadership roles include Chef/Lodge Manager, Executive Chef/General Manager, and Chef Manager, all involving team management and operational oversight in hospitality environments. These roles demonstrate clear event and hospitality supervisory experience.</t>
   </si>
   <si>
-    <t>The candidate held a Manager role at Hope Café and Catering from October 2018 to October 2019, where they managed all team members including training and conflict resolution. This indicates supervisory and leadership responsibilities in a catering environment, qualifying as relevant event or hospitality leadership experience.</t>
-  </si>
-  <si>
-    <t>The candidate currently holds the title of Catering Manager since March 2024, which is a clear leadership role in event management. Additionally, prior experience as a Trainer and in Restaurant Management involved supervising and managing teams, training staff, and overseeing operations, which supports their qualifications for supervisory roles in hospitality/events settings. The Catering Manager role alone provides over 1 year of relevant leadership experience.</t>
-  </si>
-  <si>
     <t>The candidate held the role of 'Lead Event People Manager' from April 2019 to July 2020, which explicitly indicates a leadership/supervisory role in event management. Additionally, the role of 'Lead Private Event Chef' from September 2015 to current suggests a leadership position in private event culinary management. These roles demonstrate active management and supervision in hospitality/events settings.</t>
   </si>
   <si>
     <t>The candidate has explicit supervisory and leadership experience in hospitality and events settings. They have worked as a Captain and Lead at The Party Staff since 2004, including 7 years as Captain at the Emmy Awards with Patina. They also held the role of Assistant Catering Manager at Beverly Hills Country Club from 2003-2005, which involved preparing banquet event orders and managing catering operations. Additionally, they have experience as a Catering Instructor and Bar Manager, demonstrating leadership roles in event and hospitality environments.</t>
   </si>
   <si>
-    <t>The candidate held a 'Manager' role at Texas Steakhouse &amp; Seafood from April 2010 to November 2013, where they managed front and back of house staff, handled scheduling, and inventory management. This indicates supervisory and leadership experience in a hospitality setting, qualifying them as an event/restaurant leader.</t>
-  </si>
-  <si>
     <t>The candidate held the role of Captain at Tres La Catering from 01/2017 to 05/2022, where they supervised a team of 50+ employees, coached kitchen team members, prioritized and organized tasks, demonstrated leadership by making improvements and training others, and managed operations to meet demanding objectives in a high-volume kitchen setting. This role clearly involved active management and supervisory responsibilities in a hospitality/events environment.</t>
   </si>
   <si>
@@ -1891,54 +1171,18 @@
     <t>The candidate has held multiple supervisory and managerial roles in hospitality settings, including Food and Beverage Supervisor positions at several resorts and hotels, where they oversaw multiple outlets, managed staff, coordinated events, and ensured smooth service operations. Additionally, they served as HR Assistant / Floor Supervisor at an event venue, assisting in opening and managing events with multiple bars and restaurants, and as Financial Coordinator / Events Director, creating and coordinating fundraising and educational events. These roles demonstrate leadership and supervisory experience in event and hospitality environments.</t>
   </si>
   <si>
-    <t>The candidate held the role of 'Server Captain' at Soho House from May 2018 to March 2020, which involved supervising the floor, managing employee breaks, and training new servers. This is a clear leadership/supervisory role in a hospitality setting, qualifying them for event or banquet supervisory positions.</t>
-  </si>
-  <si>
-    <t>The candidate has explicit supervisory and leadership experience in hospitality settings. As a Lead Server at Serrano Buffet from September 2022 to April 2024 (approximately 1.5 years), they were responsible for functional supervision of a team of servers, conducting shift meetings in the absence of a supervisor, and overseeing team assignments. Additionally, their current role as Shift Manager at Del Taco involves leading a team and managing daily operations, which further demonstrates supervisory experience. Although some experience is in fast food, the Lead Server role at a buffet with supervisory duties qualifies as event/banquet/restaurant leadership.</t>
-  </si>
-  <si>
-    <t>The candidate held the role of Catering Supervisor at Sodexo, Loyola Marymount University from August 2007 to July 2009, where they supervised events ranging from 2 to 2500 people, oversaw servers during setup, service, and breakdown, interacted with clients, trained new servers, and expedited food orders. This clearly demonstrates leadership and supervisory experience in a catering/events setting.</t>
-  </si>
-  <si>
-    <t>The candidate held a 'Manager Supervisor' role at Dodger Stadium from March 2016 to September 2016 (approximately 6 months) where they managed and supervised bars and food services at events, supervised employees, scheduled shifts and breaks, ensured venues were stocked, handled complaints, and trained new employees. This role clearly involved leadership and supervisory responsibilities in a hospitality/event setting, qualifying as equivalent to an Event Supervisor or Banquet Captain.</t>
-  </si>
-  <si>
-    <t>The candidate has held the role of 'Concessions/Bar Supervisor' at Legends Hospitality from 08/2019 to present (per diem) and at Levy Restaurants from 02/2019 to 11/2019. These roles involved supervising concession stands and staff at large sporting venues and special events, managing staff, training, scheduling, quality assurance, and overseeing operations, which clearly demonstrate leadership and supervisory experience in an event/hospitality setting.</t>
-  </si>
-  <si>
-    <t>The candidate held the title 'Catering Supervisor' from April 2007 to December 2009, which is a clear supervisory role in a catering/event setting. Additionally, the role 'Concessions Stand Lead' from March 2019 to December 2022 indicates leadership experience in a hospitality environment. These roles demonstrate active management and supervision responsibilities beyond standard server or bartender duties.</t>
-  </si>
-  <si>
-    <t>The candidate explicitly held the role of Banquet Captain from August 2021 to April 2022, overseeing a team of servers at wedding venues and coordinating event logistics, which is a direct supervisory leadership role in events. Additionally, the candidate was a Restaurant Manager from 2006 to 2010, a leadership role in hospitality management. These roles demonstrate relevant supervisory experience in event and hospitality settings.</t>
-  </si>
-  <si>
-    <t>The candidate has held supervisory and managerial roles explicitly in hospitality settings, including 'Food and Beverage Supervisor' positions in 2024 and 'Assistant General Manager' and 'Maitre D’/ Manager' roles. These roles involve floor management, team supervision, training, scheduling, and guest relations, which qualify as leadership/supervisory experience in event and hospitality environments.</t>
-  </si>
-  <si>
-    <t>The candidate has multiple roles explicitly titled as 'Zone Lead/Bar Manager' and 'Zone Lead/Registration' where they managed teams of bartenders and barbacks, handled scheduling, monitored alcohol policies, and managed breaks and customer disputes. These roles demonstrate leadership and supervisory responsibilities in event hospitality settings. Additionally, the 'Brand Ambassador/Team Lead' role involved team sign-in/out and break management, further confirming supervisory experience. The experience spans events primarily in 2023 and 2024, totaling approximately 1 year of relevant supervisory experience.</t>
-  </si>
-  <si>
     <t>The candidate has held supervisory and managerial roles in hospitality settings, specifically as a Supervisor at Topanga Social (Jul 2023 - Nov 2024) and Assistant Manager at Chin Chin (Jun 2021 - Jan 2024). These roles involved managing teams, scheduling staff, overseeing operations, and ensuring service quality, which aligns with leadership/supervisory responsibilities in event or food service environments. Although the titles are not explicitly 'Event Supervisor' or 'Banquet Captain,' the duties clearly reflect equivalent leadership roles in hospitality.</t>
   </si>
   <si>
     <t>The candidate has held the role of Front of House Manager at Uncle Paulie’s Deli for over 5 years, where they supervised daily shift operations, coordinated front- and back-of-house operations, and ensured service delivery and safety standards. Additionally, they worked as an Assistant Manager at Jersey Mike's Subs, leading and managing a team and overseeing store operations. These roles demonstrate explicit supervisory and leadership experience in hospitality/event settings.</t>
   </si>
   <si>
-    <t>The candidate held a Supervisor and Brand Ambassador role at Popcornopolis from 05/18 to 03/20, where they were responsible for managing event setups, booth relocation, scheduling, and payroll. This indicates leadership and supervisory responsibilities in an event-related setting, qualifying them as having relevant supervisory experience.</t>
-  </si>
-  <si>
-    <t>The candidate held a 'BOH Captain' role at NBC Sports Grill and Brew from June 2021 to February 2022, which is a supervisory leadership position. Responsibilities included managing line cooks, overseeing prep and closing tasks, covering breaks, and ensuring smooth operations, demonstrating event/restaurant leadership experience.</t>
-  </si>
-  <si>
     <t>The candidate has held multiple leadership and management roles in full service restaurant settings, including Manager, Managing Partner, and Opening Unit Manager. These roles imply supervisory and operational leadership experience in hospitality, qualifying them as equivalent to Event Supervisor or Front of House Manager roles.</t>
   </si>
   <si>
     <t>The candidate held the role of Captain/Server at C.T.I./C.B.I. Staffing Agency from May 2004 to July 2007, which is a leadership/supervisory role in event catering. The Captain role involved managing event service aspects such as set-up, breakdown, expediting, and collaboration with event managers and kitchen staff, indicating supervisory responsibilities in a hospitality/events setting.</t>
   </si>
   <si>
-    <t>The candidate held the title 'Catering Manager' at Café Kinyon &amp; Catering, which is a clear leadership/supervisory role in a catering setting. Other roles listed are primarily server or assistant positions without supervisory responsibilities.</t>
-  </si>
-  <si>
     <t>The candidate has held multiple supervisory and managerial roles in hospitality settings, including Chef Manager at Lime Catering (since June 2024), Cafe Manager at Ripe Deli, and Cold Larder Sous Chef at Auckland University of Technology. These roles involved staff management, training, rostering, and supervising kitchen and catering operations, which demonstrate leadership and supervisory experience relevant to event or hospitality management.</t>
   </si>
   <si>
@@ -1948,9 +1192,6 @@
     <t>The candidate has held supervisory and managerial roles such as Assistant Manager at Boston's Pizza (starting August 2024), Kitchen Supervisor at Hideaway Lounge (July 2019 to August 2024), and Chef/Manager/Guest Relations at San Marcos Golf Resort (January 2018 to December 2020). These roles involved managing employees, scheduling, training, overseeing food quality, and ensuring operational standards, which qualifies as leadership/supervisory experience in a hospitality setting.</t>
   </si>
   <si>
-    <t>The candidate held the role of 'Banquet Server Captain' at Chester Washington Social Club And Golf Course from 10/2021 to current, which is a supervisory leadership role in a banquet/events setting. The title 'Captain' and responsibilities such as assisting the head supervisor, maintaining event upkeep, and managing event service indicate active management and leadership in hospitality events.</t>
-  </si>
-  <si>
     <t>The candidate held a supervisory role at Balboa Yacht Club from 2014 to 2020, where they supervised support staff during weekend buffet service, managing setup, flow, and restock. This demonstrates leadership and event supervision experience in a banquet/event setting, qualifying them for roles such as Event Supervisor or Banquet Captain.</t>
   </si>
   <si>
@@ -1993,12 +1234,6 @@
     <t>The candidate has held leadership roles explicitly managing event operations and staff, such as Operations Manager - Destination Services at The Ritz Carlton Laguna Niguel, where they supervised event staff and managed hospitality and event requirements. Additionally, as Planning Manager and Sales Manager, they were responsible for overseeing event planning, client operations, and coordinating with multiple departments, demonstrating clear supervisory and managerial experience in hospitality and events.</t>
   </si>
   <si>
-    <t>The candidate held the role of Bar Supervisor at Dick Turpin, England from Aug. 2009 to Aug. 2010, where they managed bar operations including opening/closing, stocking, and cashing tills, which indicates supervisory responsibilities. Additionally, they were a Manager for Bar Crawl, Spain from Aug. 2010 to July 2011, managing operations, personnel, sales, and public relations, demonstrating leadership in a hospitality/event setting. These roles qualify as supervisory/management experience in hospitality.</t>
-  </si>
-  <si>
-    <t>The candidate held a Housekeeping Supervisor role at WorldMark by Wyndham from 03/2012 to 10/2014, which involved assigning staff, training and mentoring, scheduling, overseeing work completion, and collaborating with management. This role demonstrates leadership and supervisory experience in a hospitality setting, qualifying them as an event or hospitality supervisor equivalent.</t>
-  </si>
-  <si>
     <t>The candidate has explicit leadership roles in hospitality/events settings such as 'Banquet server lead' at Secret House Of Ivy from February 2021 to November 2023 (~2.75 years) where they coordinated with event organizers and other servers to ensure events ran smoothly. Additionally, they held an 'event lead' role through Qwick freelancers since July 2022 and a 'Janitor lead' role at ISS starting November 2024, which involves team coordination and training. The banquet server lead and event lead roles demonstrate supervisory experience in banquet/event settings, qualifying them for event supervisory or banquet captain roles.</t>
   </si>
   <si>
@@ -2008,48 +1243,18 @@
     <t>The candidate has held multiple supervisory and managerial roles in hospitality settings, including Food and Beverage Supervisor, Restaurant Supervisor, Restaurant Manager, and Banquet Manager. They have experience managing staff, overseeing events according to Banquet Event Orders, coordinating with culinary and banquet teams, and leading front-of-house operations. Their experience as Banquet Manager and Event Coordinator explicitly involves event leadership and supervision. Overall, their 25 years of experience include significant leadership roles in event and hospitality management.</t>
   </si>
   <si>
-    <t>The candidate explicitly held the title 'Banquet Supervisor' at Spaghetti Factory for 2 years, where they supervised banquet events and coordinated staff to ensure smooth event execution. This role demonstrates direct leadership and supervisory experience in a hospitality event setting.</t>
-  </si>
-  <si>
     <t>The candidate has held the role of Director of Catering &amp; F&amp;B since 2016, leading end-to-end catering and hospitality operations for events, including on-site execution and team direction. This clearly demonstrates supervisory and leadership experience in event and catering management, qualifying them for roles such as Event Supervisor, Banquet Captain, or Catering Manager.</t>
   </si>
   <si>
-    <t>The candidate held the explicit role of 'Event Supervisor' at Go Staff from March 2023 to February 2025, which is a leadership position in an event setting. Their responsibilities included supervising employees, ensuring safety compliance, and managing equipment setup, demonstrating relevant supervisory experience in hospitality/events.</t>
-  </si>
-  <si>
-    <t>The candidate held a Restaurant Manager role from August 2017 to January 2020, which involved leading daily operations, recruiting, training, and supervising staff. This demonstrates supervisory and leadership experience in a hospitality setting, qualifying as equivalent to roles like Event Supervisor or Front of House Manager.</t>
-  </si>
-  <si>
     <t>The candidate held a 'Lead server' role at The Party Staff, Inc. from 10/2008 to 05/2020, where they supervised a team of servers during high-volume events. This indicates leadership and supervisory experience in an event hospitality setting, qualifying them as an event supervisor or equivalent.</t>
   </si>
   <si>
-    <t>The candidate held a 'Bartender/Manager' role at Riders Smokehouse from October 2019 to June 2022, where they hired staff, maintained schedules, and managed bookings, indicating leadership and supervisory responsibilities in a hospitality setting. Additionally, the resume mentions 'Shift management' and 'Supervising experience' skills, supporting their qualification for a supervisory or managerial role in hospitality/events.</t>
-  </si>
-  <si>
-    <t>The candidate has explicit supervisory experience as an 'Assistant Event Lead' at Fever Events, where they supervise front-of-house staff, manage guest check-in, seating, and crowd movement, and support event operations including setup, execution, and breakdown. This role involves leadership and operational responsibilities in an event setting, meeting the criteria for event supervisory experience.</t>
-  </si>
-  <si>
-    <t>The candidate held the position of Floor Manager at L’Antica Pizzeria Da Michele from 05/2019 to 01/2020, which is a supervisory/leadership role in a hospitality setting. This role involved managing inventory, improving customer satisfaction, fostering teamwork, and participating in management meetings, indicating leadership responsibilities. Although the experience is less than a year, it qualifies as relevant supervisory experience.</t>
-  </si>
-  <si>
     <t>The candidate held the role of Food Service Supervisor at Redwood Steakhouse and Brewery from May 2021 to June 2024, which is a supervisory leadership position in a hospitality/food service setting. Additionally, the Lead Bartender role at Chili's likely involved team leadership responsibilities. These roles demonstrate experience managing or supervising event or restaurant teams, qualifying them for event supervisory or banquet captain equivalent roles.</t>
   </si>
   <si>
-    <t>The candidate held the role of Front of House Supervisor at Salt and Spoon from January 2024 to September 2025, which is a leadership position involving scheduling, training, maintaining standards, and collaborating with ownership to improve service efficiency. This clearly qualifies as a supervisory/management role in a hospitality setting. Other roles listed are primarily server positions or a shift supervisor in a coffee shop, which does not meet the event or banquet leadership criteria.</t>
-  </si>
-  <si>
     <t>The candidate held a 'House Supervisor/Charge RN' role at Pioneer Valley Hospital for nearly 5 years, which involved supervisory responsibilities such as handling staffing and managing issues as they arose. Additionally, the resume states 'Previous management experience front of house for a busy restaurant' and 'Previous experience managing a winery,' indicating leadership roles in hospitality settings. Although the hospital role is healthcare-focused, the supervisory experience is relevant, and the hospitality management experience is explicitly mentioned, qualifying the candidate for event or front of house supervisory roles.</t>
   </si>
   <si>
-    <t>The candidate held the role of F&amp;B Shift Supervisor at Talkeetna Alaskan Lodge for approximately 4 months (June 2025 - October 2025). This role involved directing front-of-house operations during high-volume shifts, training and mentoring staff, optimizing service flow, and coordinating between departments, which clearly demonstrates leadership and supervisory responsibilities in a hospitality setting. Other roles such as Closing Shift Manager and Shift Manager were in fast food or general restaurant settings but do not specifically relate to event, banquet, or catering leadership.</t>
-  </si>
-  <si>
-    <t>The candidate held the role of Front of House Supervisor at LOGE Camps Glacier from October 2024 to March 2026, which is a clear supervisory position in a hospitality setting. Additionally, they were a Front of House Key Holder at Baumhower’s Victory Grille from November 2022 to January 2024, where they supervised and trained staff, supporting and guiding them to ensure performance. These roles demonstrate leadership and supervisory experience in hospitality/event environments.</t>
-  </si>
-  <si>
-    <t>The candidate held a leadership role as 'Lead Bartender / Manager' and 'Front-of-House Manager' at Wailea Kitchen from 2021 to 2022, where they managed employee scheduling, payroll, onboarding, vendor relations, and overall front-of-house operations. This role demonstrates supervisory and management experience in a hospitality setting, qualifying as an equivalent leadership role.</t>
-  </si>
-  <si>
     <t>The candidate has held multiple leadership roles such as Field Manager, Team Lead, Project Manager, and Assistant Project Manager in event, tradeshow, and promotional settings from approximately 2015 to 2022. These roles involved managing teams, scheduling, client relations, and overseeing event execution, which align with supervisory and leadership responsibilities in hospitality and events. Although not explicitly titled 'Event Supervisor' or 'Banquet Captain', the roles and responsibilities clearly demonstrate equivalent leadership experience in event management.</t>
   </si>
   <si>
@@ -2059,12 +1264,6 @@
     <t>The candidate held a Supervisor role at The Goat &amp; Vine from February 2019 to February 2023, where they guided all front of house employees, resolved employee and guest conflicts, and managed opening and closing of the restaurant daily. This demonstrates leadership and supervisory experience in a hospitality setting equivalent to a Front of House Manager.</t>
   </si>
   <si>
-    <t>The candidate currently holds the title of Event Supervisor at Sodexo since 2023, explicitly supervising front- and back-of-house teams for large-scale events, coordinating staff and service flow, and managing operational issues. Additionally, as a Stand Lead at Levy Restaurants, they supervised concession stand operations and staff during peak events. These roles demonstrate clear leadership and supervisory experience in event and hospitality settings.</t>
-  </si>
-  <si>
-    <t>The candidate has explicit experience as an Event Supervisor at Legends Hospitality from 2022 to present, where they supervised staff across catering and hospitality events, coordinated team assignments, and managed operational flow. Additionally, as a Stand Lead at Levy Restaurants, they supervised team members and assigned roles during high-capacity events. These roles demonstrate leadership and supervisory responsibilities in event and hospitality settings.</t>
-  </si>
-  <si>
     <t>The candidate has explicit supervisory and leadership experience in hospitality settings. As a Floor Captain (Lead Server), they managed floor plans, coordinated staff, reviewed event orders, and handled large events up to 1500 people. Additionally, their roles as General Manager and Assistant General Manager involved hiring, training, supervising staff, managing operations, and leading teams in restaurant environments. These roles clearly demonstrate event and hospitality leadership beyond standard server or bartender duties.</t>
   </si>
   <si>
@@ -2074,33 +1273,18 @@
     <t>The candidate has held leadership roles such as Executive Chef / Owner and Kitchen Manager, where they managed teams including front of house staff and were responsible for executing large client events. These roles involved supervisory and management duties in a hospitality setting, including event coordination and team leadership, which qualifies as equivalent leadership/supervisory experience.</t>
   </si>
   <si>
-    <t>The candidate held the role of Banquet Captain at Santa Monica Proper Hotel from November 2021 to September 2024, which is an explicit leadership/supervisory position in a banquet/event setting. Responsibilities such as setting up and breaking down banquet equipment, guest support, and inventory management indicate active management and supervision of banquet events.</t>
-  </si>
-  <si>
-    <t>The candidate held a 'Head Server' position at AVAMERE Retirement Home where they were responsible for training and leading a team of servers, managing staff in the absence of the manager, scheduling employees, and resolving staff issues. This role involved active supervision and leadership in a hospitality setting, which qualifies as an equivalent leadership/supervisory role.</t>
-  </si>
-  <si>
     <t>The candidate has held leadership roles such as Banquet Captain and Banquet &amp; Event Lead, explicitly managing banquet and event service teams at large luxury events. Additionally, as Director of Beverage Operations, they lead beverage operations and staff training, demonstrating supervisory and management experience in hospitality settings.</t>
   </si>
   <si>
     <t>The candidate has held multiple supervisory and managerial roles in hospitality settings, including Manager at Panera Bread since February 2023, Supervisor at Famous Nathan's Restaurant from January to August 2023, and Team Lead at Red Lobster from March 2019 to May 2022. These roles involved managing staff, overseeing operations, and leading teams, which aligns with leadership/supervisory experience in hospitality or events settings.</t>
   </si>
   <si>
-    <t>The candidate explicitly states having former General Manager and Restaurant Manager roles in full-service dining environments, which are leadership positions involving management and supervision. Although no specific years are provided, these titles qualify as supervisory roles in hospitality.</t>
-  </si>
-  <si>
     <t>The candidate has explicit leadership and supervisory experience in hospitality settings, including roles as Front of House Manager at California Pizza Kitchen (June 2016 - January 2019) where they managed servers, hosts, bartenders, and takeout teams, and as General Manager and Assistant General Manager in restaurant environments overseeing staff management, scheduling, training, and operations. These roles clearly involve managing and leading event or restaurant teams, meeting the criteria for event supervisory or equivalent leadership roles.</t>
   </si>
   <si>
     <t>The candidate has held multiple leadership roles such as Lead Server, Shift Manager, and Lead Hostess in hospitality settings. These roles involved managing restaurant operations, staff oversight, training new hires, and supervising front desk operations, which demonstrate supervisory and leadership responsibilities in event and hospitality environments.</t>
   </si>
   <si>
-    <t>The candidate held a role as a Bar Apprentice where they explicitly supervised the work of bar staff, including other bartenders, which indicates leadership and supervisory responsibilities in a hospitality setting. This experience spans from November 2021 to May 2024, approximately 2.5 years. Although the title is not a standard event leadership title, the supervisory duties in a bar environment qualify as relevant leadership experience.</t>
-  </si>
-  <si>
-    <t>The candidate held the position of Bar Manager at Lucille's Smokehouse from November 2018 to June 2020, where they managed all employees of the restaurant, handled disciplinary actions, ensured smooth operations, and managed emergencies. This role demonstrates leadership and supervisory responsibilities in a hospitality setting, qualifying as an equivalent leadership role.</t>
-  </si>
-  <si>
     <t>The candidate has 12 years as a Banquet Captain and 2 years as an Assistant Banquet Manager, both of which are supervisory leadership roles in banquet/event settings. Additionally, the role of Captain at Renaissance Nashville Hotel for over 12 years indicates event team leadership experience.</t>
   </si>
   <si>
@@ -2110,54 +1294,27 @@
     <t>The candidate held the role of Banquet Captain at Hyatt Vineyard Creek Hotel and Spa for 5 years, where they supervised servers, scheduled staff, attended meetings, and ensured event success, which is a direct leadership role in event management. Additionally, they worked as a Diningroom Supervisor for 4 years, managing scheduling and staff, and as a Restaurant Manager in multiple locations, which also involved supervisory responsibilities. These roles clearly demonstrate leadership and supervisory experience in hospitality and events.</t>
   </si>
   <si>
-    <t>The candidate held the role of Show Manager where they coordinated live event logistics, acted as liaison between performers, venues, and technical teams, which indicates event leadership. Additionally, as House Manager, they oversaw daily operations, staff supervision, scheduling, and front-of-house systems, demonstrating supervisory and management experience in a hospitality setting. These roles clearly show leadership and supervisory responsibilities in event and hospitality environments.</t>
-  </si>
-  <si>
-    <t>The candidate has held leadership roles such as Assistant Manager and Supervisor in hospitality settings, overseeing daily restaurant operations, supervising and coordinating teams of 10+ staff, resolving operational challenges, and conducting training programs. These responsibilities demonstrate active management and supervisory experience in a hospitality environment, qualifying them for event supervisory or banquet captain equivalent roles.</t>
-  </si>
-  <si>
     <t>The candidate held the role of Event Coordinator from May 2020 to March 2026, where they directed logistics, planning, and execution of various events, managed on-site troubleshooting, vendor schedules, and served as the primary onsite event coordinator. This clearly demonstrates leadership and supervisory responsibilities in an event setting. Additionally, as Lead Server from June 2017 to May 2020, they led front of house staff, conducted pre-shift meetings, assigned sections, and managed dining room flow, indicating supervisory experience in a banquet/fine dining environment.</t>
   </si>
   <si>
-    <t>The candidate held a Supervisor role at Brenden Theatres from January 2023 to December 2024, where they supervised daily operations, trained and supported staff, managed customer service issues, and ensured safety and protocol adherence. This demonstrates leadership and supervisory experience in a hospitality-related environment, qualifying them for event or front-of-house management roles.</t>
-  </si>
-  <si>
     <t>The candidate has repeatedly led teams of 5 employees in daily operations and procedures across multiple hospitality roles (bartender and waitress positions) from July 2020 to the present. They provided training, ensured service quality, managed inventory, and handled operational oversight. These responsibilities demonstrate supervisory and leadership experience in hospitality settings, qualifying them as an Event Supervisor/Banquet Captain/Front of House Manager equivalent.</t>
   </si>
   <si>
     <t>The candidate has explicit leadership and supervisory experience in hospitality and events settings. They worked as a Catering Manager from 2007-2013 (6 years) managing catering programs, training staff, and coordinating events. They also held a Restaurant Manager role for nearly a year managing front and back of house operations, staff recruitment, scheduling, and catering. Additionally, they were an Event Coordinator for 2 years organizing and planning events. These roles demonstrate active management and leadership in event and hospitality environments.</t>
   </si>
   <si>
-    <t>The candidate has held supervisory and leadership roles in hospitality settings, including 'Shift Supervisor / Assistant General Manager' at Armani Caffe and 'Barista Shift Supervisor' at Juliette’s Cafe. These roles involved supervising daily operations, employee scheduling, training staff, coaching employees, and resolving issues, which demonstrate active management and leadership responsibilities in a hospitality environment.</t>
-  </si>
-  <si>
-    <t>The candidate held the role of Banquet Captain at Great Wolf Lodge from December 2022 to January 2025, which is a supervisory leadership position in a banquet/event setting. Responsibilities included setting up events, managing servers, ensuring event flow, client communication, creating reports, and working with the sales team, all indicating active management and leadership in hospitality events.</t>
-  </si>
-  <si>
-    <t>The candidate has held the role of 'Team Lead/Brand Ambassador' at multiple companies from September 2021 to current (2023), which involves managing groups of brand ambassadors and leading teams to client requests. This demonstrates supervisory and leadership experience in event or activation settings, which is equivalent to roles like Event Supervisor or Front of House Manager.</t>
-  </si>
-  <si>
-    <t>The candidate has held a 'Team Lead' position at The General Store during Goldenvoice festivals such as Coachella, where they managed the location, ensured team members took breaks, and handled other supervisory duties. This indicates leadership and supervisory experience in an event setting, qualifying them as an event supervisor equivalent.</t>
-  </si>
-  <si>
     <t>The candidate has held the role of Owner / Head Chef / Restaurant Manager since May 2019, managing day-to-day restaurant operations including staffing, scheduling, and supervising kitchen and service staff. They also led catering events and high-volume service, demonstrating leadership and supervisory experience in a hospitality setting. This qualifies as equivalent to an Event Supervisor or Catering Manager role.</t>
   </si>
   <si>
     <t>The candidate has held multiple senior leadership roles in hospitality and event settings, including Executive Chef positions at large venues such as the Getty Center, Los Angeles Memorial Coliseum, and SoFi Stadium. These roles involved managing large teams, overseeing catering and event operations, and directly supervising staff and event execution. The Executive Kitchen Manager role at The Cheesecake Factory also involved supervisory responsibilities. Although the titles are culinary-focused, the scope of responsibilities clearly includes event leadership and team supervision in hospitality settings.</t>
   </si>
   <si>
-    <t>The candidate held the role of 'Captain' at Four Seasons/Charlie Palmers Steakhouse, where they managed a team throughout customers' fine dining experience and provided high-level service. This is a supervisory leadership role in a hospitality setting, qualifying them as an Event Supervisor/Banquet Captain equivalent. However, the resume does not specify the duration of this role, so years of experience cannot be accurately determined.</t>
-  </si>
-  <si>
     <t>The candidate held a 'Floor Supervisor' role at Spin Neapolitan Pizza from January 2013 to December 2015, which involved team leadership, training, and supervisory responsibilities in a hospitality setting. This role qualifies as a leadership/supervisory position in a restaurant environment.</t>
   </si>
   <si>
     <t>The candidate has held the role of 'Shift Leader' at Marriott Irvine Spectrum and Michael Kors Distributors, where they supervised line cooks and prep staff, managed scheduling, training, and workflow efficiency, and led kitchen operations during service. This demonstrates leadership and supervisory experience in a hospitality setting, including banquet-related work. Although the title is not explicitly 'Event Supervisor' or 'Banquet Captain,' the responsibilities align with equivalent supervisory roles in events and hospitality.</t>
   </si>
   <si>
-    <t>The candidate held the explicit role of Banquet Manager at 8 Bit Brewing Company from April 2017 to June 2018, where they planned and executed banquet menus, coordinated prep and service, collaborated with clients, managed inventory, and enforced food safety procedures. This role clearly involved leadership and supervisory responsibilities in an event/banquet setting, meeting the criteria for event supervisory experience.</t>
-  </si>
-  <si>
     <t>The candidate held leadership roles such as 'Stand Lead' at Aramark where they led bar operations, managed inventory, coordinated the team, and trained staff, which qualifies as supervisory experience in a hospitality events setting. Additionally, the 'Spa Manager' role involved managing spa operations and staff, further demonstrating supervisory experience. These roles combined provide over three years of relevant leadership experience.</t>
   </si>
   <si>
@@ -2179,9 +1336,6 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/hpdys94nlr8b6z3k_MarroquinCordero_David_20240229065401.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/bc8v8zb345udnsai_JFColsonResume.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/yid0za2s8wh4huq2_Oscar_Apodaca.pdf</t>
   </si>
   <si>
@@ -2203,9 +1357,6 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/g88eza9k4c8feuws_Carmen%20Madani%20Resume.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/vsn0x5kms4rk51m0_1656564075538-JeanneCurtis.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/n7zuck5wsrpf55ea_Resume%202024_August.pages%20%281%29.pdf</t>
   </si>
   <si>
@@ -2215,24 +1366,9 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/7dhr90ss9zrxhzmt_resume_6633fb217c10c.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/klihf3yjtvjpt761_resume2024.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/xr3nsziglt1nbwhb_Cecilia_Marquez_resume%20022426.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/qlox5jnhctwjk4ws_Raynes_Daniela_20221114212646.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/o8gmc18xjf65vuph_1NEW20AND20INPROVED20RESUME.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/iu1hbr2abr3eide7_Bunn_William_20221116201244.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/f2tylruhr5omwkud_AL%202025.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/wgsvjnmfy5at79ec_Christopher-Terry.pdf</t>
   </si>
   <si>
@@ -2248,15 +1384,9 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/1ods2zblicimfw52_Jong%2520Moon%2520Lu%2520resume%25202025%2520food%2520service%2520-%2520edited.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/59p8eee38qan31e0_Ortega_Leroy_20230303000945.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/l8ufwtoxobasvwuw_resume_641f590775f4a.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/hzr3qle043ax4v8o_resume_6489324d5926f.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/zrgj0nppt3vfr9ts_SCOTTMITCHELL_TERRY_20230706161128.pdf</t>
   </si>
   <si>
@@ -2269,18 +1399,6 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/tx4ecnk4ugi8tv9i_Rubalcaba_Robert_20230822234235.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/1y7tgz0znj38cnqn_GutierrezJr_Victor_20230916164619.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/ru0qc97eusn74zgc_Mathews_Amera_20230910051632.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/2dtspb5kku03phb5_Dinneen_Molly_20231010141420.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/fce5hz4y6jnu21l7_Mitchell_Vanessa_20231129172839.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/9ev1gt0co4yi2x2b_Miller_Xavier_20231203233811.pdf</t>
   </si>
   <si>
@@ -2293,27 +1411,15 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/5uv0ym8zv2sh6ozj_resume_65b2b1812c050%20%281%29.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/19i9w5qk0a1rk9rg_Duke_Terence_20240227162734.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/lhemu4ib5rsjr37n_Garland_Shey_20240227010337.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/0ds8ws40ulnp45ue_Zuniga_Maria_20240319023827.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/w4mfatit2e6b8qsf_IndeedResume.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/lztlmnpjdwa20ep4_Arnold_Alisha_20240514201408.pdf</t>
   </si>
   <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/6pfkr8vljzy9vpbm_resume_664e52a268958.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/uw6bnwbflxvxe545_Tep_Vandarith_20240618025944.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/d8t0ixdnb5lxbqob_Erica%20New%20Resume.pdf</t>
   </si>
   <si>
@@ -2323,54 +1429,18 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/amg4ej6nx2opikwi_Silva_Amberlyn_20240730002700.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/2lfnwv7mjx131egg_0bb6db1e_20240820154324eo9PxHkCnd%20%281%29.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/3aj8jvszzqyhjot5_%2520Resume%25202026.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/fl6e8ay5k0y3zdur_Gil_Ruben_20240814102834.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/iyqy9wtbixhxnasu_Huggett_Karen_20240821004547.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/iads6ef3m62zhap0_8338181_Fred_Torres_ResumeUpload.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/5rtzcvcb8uw8zqx2_-VVerbeckSkillsResumeFinal-.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/a4g36xwx57nc0mic_SamiraZeruk%20%281%29.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/n1folppz4zvl4vf3_FOUZIA%20BURFIELD%20res111.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/zrucfim0fytpoa1o_event.brandambassador.resume10.31.24.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/m631feat9s2wc2vt_Resume%25202025.docx</t>
   </si>
   <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/uekwzs57blwwh4xf_Freitag%20Michael%20A.%20CV2024.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/9lalp78py0m6wbxu_Resume%252520doc-1-70a12eee3e274addbf25ddeb5d8e939d.docx</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/07uycg193ojw2ntv_Resume%202025.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/plwj0y5zima843of_My%20Resume.pdf</t>
   </si>
   <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/4smezeqvnixtuii5_Elias-Welsh.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/7ho8xqxge2ssfua8_Melanie%2520Sampson_Catering%25202026.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/jcwiet5cwhdysuju_Geo%20Mangiaterra%20CV.pdf</t>
   </si>
   <si>
@@ -2380,9 +1450,6 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/3fzdh5em6jin54ro_Resume%20%287%29.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/wux34403m48opsoz_Tiara_Mitchell_Resume.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/gokfw6craj7297pw_Andrew%20Powitzky%20Resume.pdf</t>
   </si>
   <si>
@@ -2425,12 +1492,6 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/u41t4dkoil1vkwdc_Nancy%20Shugg_Resume.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/i1kcg21oxwq887m8_Leigh%20Pollitt_Resume.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/xi3wsb0hjcxdomi0_Best%2520Resume%2520.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/24gmxot70io9yutv_8545635_C%C3%A9sar_Munguia_ResumeUpload.pdf</t>
   </si>
   <si>
@@ -2440,48 +1501,18 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/pjf6cyz98sc0mmyy_8559422_Amber_L_Denman_ResumeUpload.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/oy94yi2exlf4tjqk_Evan_Spriggs_Combined_Resume.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/dhbhd33m45fib5dd_SSCHREMAY26.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/vefsvz1wjk4bea50_Cameron%20Allen_Resume.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/z82xcrj95symf7o4_Stephanie_Hass_Private_Chef_Resume.docx</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/99581c4t5t4o4gvi_NatsResume_1_26d.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/qsdcrmj53x1xz4ry_Laura%20Coder_Resume.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/3z765u13brjv0e4u_Work%2520Resume%2520Dec%252025.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/qx8lyb759u7kr8q8_Ricardo%2520Pichardo%2520resume.docx</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/keaqs2fr6yrxd46w_Emery%20Pierce_Resume.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/mbkmpos1xp7adrfn_Alexis%20Diamond%20Resume.Updated.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/9ddg3nw0art6ayn8_Celeste%20Crowellpdfres.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/yrilcdjwu705jfgo_Brian%20Burns_Resume.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/zp4c7qax5s67d4i8_Resume.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/aemkee8u2sx4gpn9_Kalei%20Castillon%20Resume%202026.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/oajyjrnr4s70yphh_KathyNguyen.pdf</t>
   </si>
   <si>
@@ -2491,12 +1522,6 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/9r38kulq4w0hnbvw_Madison%20Stephan_Resume.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/ombxcq4y58y0sl00_Victoria%20Franciscous%20Hospitality.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/2ynzemrtfsl4erss_Thrasius%20Duncan%20Resume.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/w9prizfn11hiobz1_2026_Food_Beverage_Hospitality.pdf</t>
   </si>
   <si>
@@ -2506,33 +1531,18 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/2n9ga0l9cxnnubgu_Chef_Shieya_Resume.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/bzjnmdnnhjsdxvrw__Resume%202026.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/x9n35a3pk1xsjobx_Resume%204.11.2024.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/bmb7r9unhtv2fq5b_Ryan_Foltz_Resume_Final_0322.pdf</t>
   </si>
   <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/u7ruwqiz8a50cntm_Resume.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/hn88hx8dd9whragc_Travis_Jones_Bartender_Craft_Upscale.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/avv7fvy6ibes8lj4_Resume.pdf</t>
   </si>
   <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/hobva0w8wzg42cs7_Meagan%20Wise%20Resume.%20PDF.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/updoeaolm3n0h3hi_Resume%2520for%2520jobs.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/mefkw451npfv6pwi_Brett%20King_Resume.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/gh74c7evwnvmxytm_NAJIMA%2520GRAHAM.pdf</t>
   </si>
   <si>
@@ -2542,52 +1552,25 @@
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/xxeebkcklcb4ylgg_Rosa%20Madriz_Resume.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/ukh6z31boztjk2ty_Resume%20%282%29.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/kbpzeoqh5pgjrxpq_Abad%2C%20Jasmine%20FnB.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/kamwlz30cgeedwso_Tara%2520Resume%25202026.docx</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/hc8xf7obk7vl29i8_Stephanie%20Rodriguez%20gomez_Resume.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/gkamjo5anobcc7rv_Pdf26resumeks.pdf.pdf</t>
   </si>
   <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/l7ybaoh2126l9lgh_Jacqueline-Resume2023.docx</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/06xydwxi3qtwsgh3_Nan_Luh%20resume%20.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/v5fx4q9ver1phemu_Copy%20of%20resume.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/k0adys3u4r3avunn_Drew%2520mergens%2520ba%2520resume%252012-3-25.pdf.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/7gj06yiqcspewzae_Schae%2520Beaudoin%2520Service%2520Resume.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/za4jek8g6mftznup_Resume%20pdf.pdf</t>
   </si>
   <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/qsx8inl4jx541dcg_John%20Brenning%20Resume.pdf</t>
   </si>
   <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/6k4y51h96nqzgvjg_C7F750B6.pdf</t>
-  </si>
-  <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/3ag4fsgvrpl1ynwt_RESUME%25202025%2520%281%29%2520%282%29.docx</t>
   </si>
   <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/sxq17ehzgvlguyot_Alberto%20Ayala%20Resume%202025.pdf</t>
-  </si>
-  <si>
-    <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/et6s0j4g352dnw5u_ResumeRischelleUrbanUpdated2026.pdf</t>
   </si>
   <si>
     <t>https://web-application-files.s3.us-east-1.amazonaws.com/employee/resume/p5y60gyx8frefhjf_Jennifer_Vigneault_Resume.pdf</t>
@@ -2674,7 +1657,50 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2685,6 +1711,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2974,10 +2004,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -3018,3896 +2048,2333 @@
         <v>44206</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>243</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>387</v>
+        <v>239</v>
       </c>
       <c r="E2" t="s">
-        <v>524</v>
+        <v>321</v>
       </c>
       <c r="F2">
         <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>660</v>
+        <v>405</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>804</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>17704</v>
+        <v>36174</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>301</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>445</v>
+        <v>303</v>
       </c>
       <c r="F3">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>574</v>
+        <v>384</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>718</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>36174</v>
+        <v>45717</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>218</v>
+        <v>175</v>
       </c>
       <c r="D4" t="s">
-        <v>362</v>
+        <v>261</v>
       </c>
       <c r="E4" t="s">
-        <v>502</v>
+        <v>341</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>635</v>
+        <v>427</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>779</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>45717</v>
+        <v>19495</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>289</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>433</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
-        <v>564</v>
+        <v>275</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>706</v>
+        <v>355</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>850</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>19495</v>
+        <v>20959</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>306</v>
+        <v>192</v>
       </c>
       <c r="E6" t="s">
-        <v>450</v>
+        <v>278</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>579</v>
+        <v>358</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>723</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>20959</v>
+        <v>21120</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>310</v>
+        <v>194</v>
       </c>
       <c r="E7" t="s">
-        <v>454</v>
+        <v>280</v>
       </c>
       <c r="F7">
         <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>583</v>
+        <v>360</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>727</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>21120</v>
+        <v>40236</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>312</v>
+        <v>228</v>
       </c>
       <c r="E8" t="s">
-        <v>456</v>
+        <v>311</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>585</v>
+        <v>394</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>729</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>40236</v>
+        <v>45417</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>230</v>
+        <v>168</v>
       </c>
       <c r="D9" t="s">
-        <v>374</v>
+        <v>254</v>
       </c>
       <c r="E9" t="s">
-        <v>512</v>
+        <v>334</v>
       </c>
       <c r="F9">
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>647</v>
+        <v>420</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>791</v>
+        <v>506</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>45417</v>
+        <v>21021</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>275</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>419</v>
+        <v>193</v>
       </c>
       <c r="E10" t="s">
-        <v>553</v>
+        <v>279</v>
       </c>
       <c r="F10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="G10" t="s">
-        <v>692</v>
+        <v>359</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>836</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>21021</v>
+        <v>21923</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>311</v>
+        <v>198</v>
       </c>
       <c r="E11" t="s">
-        <v>455</v>
+        <v>284</v>
       </c>
       <c r="F11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>584</v>
+        <v>364</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>728</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>21607</v>
+        <v>43340</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s">
-        <v>318</v>
+        <v>234</v>
       </c>
       <c r="E12" t="s">
-        <v>461</v>
+        <v>317</v>
       </c>
       <c r="F12">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>591</v>
+        <v>400</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>735</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>21923</v>
+        <v>18503</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>321</v>
+        <v>185</v>
       </c>
       <c r="E13" t="s">
-        <v>464</v>
+        <v>271</v>
       </c>
       <c r="F13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="G13" t="s">
-        <v>594</v>
+        <v>351</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>738</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>43340</v>
+        <v>23464</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>236</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>380</v>
+        <v>204</v>
       </c>
       <c r="E14" t="s">
-        <v>518</v>
+        <v>290</v>
       </c>
       <c r="F14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>653</v>
+        <v>370</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>797</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>18503</v>
+        <v>24734</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>302</v>
+        <v>209</v>
       </c>
       <c r="E15" t="s">
-        <v>446</v>
+        <v>266</v>
       </c>
       <c r="F15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>575</v>
+        <v>375</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>719</v>
+        <v>461</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>23464</v>
+        <v>44738</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="D16" t="s">
-        <v>329</v>
+        <v>241</v>
       </c>
       <c r="E16" t="s">
-        <v>472</v>
+        <v>323</v>
       </c>
       <c r="F16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="G16" t="s">
-        <v>602</v>
+        <v>407</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>746</v>
+        <v>493</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>24734</v>
+        <v>15106</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>338</v>
+        <v>181</v>
       </c>
       <c r="E17" t="s">
-        <v>440</v>
+        <v>267</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>611</v>
+        <v>347</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>755</v>
+        <v>433</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>44738</v>
+        <v>18921</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>248</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>392</v>
+        <v>186</v>
       </c>
       <c r="E18" t="s">
-        <v>529</v>
+        <v>272</v>
       </c>
       <c r="F18">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>665</v>
+        <v>352</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>809</v>
+        <v>438</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>15106</v>
+        <v>24670</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>297</v>
+        <v>208</v>
       </c>
       <c r="E19" t="s">
-        <v>441</v>
+        <v>294</v>
       </c>
       <c r="F19">
         <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>570</v>
+        <v>374</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>714</v>
+        <v>460</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>18921</v>
+        <v>27272</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
-        <v>303</v>
+        <v>212</v>
       </c>
       <c r="E20" t="s">
-        <v>447</v>
+        <v>297</v>
       </c>
       <c r="F20">
         <v>10</v>
       </c>
       <c r="G20" t="s">
-        <v>576</v>
+        <v>378</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>720</v>
+        <v>464</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>24670</v>
+        <v>41752</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="D21" t="s">
-        <v>337</v>
+        <v>231</v>
       </c>
       <c r="E21" t="s">
-        <v>480</v>
+        <v>314</v>
       </c>
       <c r="F21">
         <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>610</v>
+        <v>397</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>754</v>
+        <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>27272</v>
+        <v>43387</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D22" t="s">
-        <v>344</v>
+        <v>236</v>
       </c>
       <c r="E22" t="s">
-        <v>486</v>
+        <v>318</v>
       </c>
       <c r="F22">
         <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>617</v>
+        <v>402</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>761</v>
+        <v>488</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>41752</v>
+        <v>45469</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>233</v>
+        <v>170</v>
       </c>
       <c r="D23" t="s">
-        <v>377</v>
+        <v>256</v>
       </c>
       <c r="E23" t="s">
-        <v>515</v>
+        <v>336</v>
       </c>
       <c r="F23">
         <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>650</v>
+        <v>422</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>794</v>
+        <v>508</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>43387</v>
+        <v>43352</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>238</v>
+        <v>149</v>
       </c>
       <c r="D24" t="s">
-        <v>382</v>
+        <v>235</v>
       </c>
       <c r="E24" t="s">
-        <v>519</v>
+        <v>298</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="G24" t="s">
-        <v>655</v>
+        <v>401</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>799</v>
+        <v>487</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>45469</v>
+        <v>23313</v>
       </c>
       <c r="B25" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>277</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>421</v>
+        <v>202</v>
       </c>
       <c r="E25" t="s">
-        <v>555</v>
+        <v>288</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G25" t="s">
-        <v>694</v>
+        <v>368</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>838</v>
+        <v>454</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>43352</v>
+        <v>44515</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="D26" t="s">
-        <v>381</v>
+        <v>240</v>
       </c>
       <c r="E26" t="s">
-        <v>487</v>
+        <v>322</v>
       </c>
       <c r="F26">
-        <v>9.3000000000000007</v>
+        <v>8</v>
       </c>
       <c r="G26" t="s">
-        <v>654</v>
+        <v>406</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>798</v>
+        <v>492</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>23100</v>
+        <v>45284</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D27" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="E27" t="s">
-        <v>469</v>
+        <v>332</v>
       </c>
       <c r="F27">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G27" t="s">
-        <v>599</v>
+        <v>418</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>743</v>
+        <v>504</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>23313</v>
+        <v>21906</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>183</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>327</v>
+        <v>197</v>
       </c>
       <c r="E28" t="s">
-        <v>470</v>
+        <v>283</v>
       </c>
       <c r="F28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" t="s">
-        <v>600</v>
+        <v>363</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>744</v>
+        <v>449</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>44515</v>
+        <v>23635</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>245</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>389</v>
+        <v>205</v>
       </c>
       <c r="E29" t="s">
-        <v>526</v>
+        <v>291</v>
       </c>
       <c r="F29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G29" t="s">
-        <v>662</v>
+        <v>371</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>806</v>
+        <v>457</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>45284</v>
+        <v>24461</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>271</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>415</v>
+        <v>207</v>
       </c>
       <c r="E30" t="s">
-        <v>549</v>
+        <v>293</v>
       </c>
       <c r="F30">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="G30" t="s">
-        <v>688</v>
+        <v>373</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>832</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>21906</v>
+        <v>26039</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s">
-        <v>320</v>
+        <v>210</v>
       </c>
       <c r="E31" t="s">
-        <v>463</v>
+        <v>295</v>
       </c>
       <c r="F31">
         <v>7</v>
       </c>
       <c r="G31" t="s">
-        <v>593</v>
+        <v>376</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>737</v>
+        <v>462</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>23635</v>
+        <v>39306</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="D32" t="s">
-        <v>330</v>
+        <v>224</v>
       </c>
       <c r="E32" t="s">
-        <v>473</v>
+        <v>307</v>
       </c>
       <c r="F32">
         <v>7</v>
       </c>
       <c r="G32" t="s">
-        <v>603</v>
+        <v>390</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>747</v>
+        <v>476</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>24461</v>
+        <v>45041</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="D33" t="s">
-        <v>336</v>
+        <v>244</v>
       </c>
       <c r="E33" t="s">
-        <v>479</v>
+        <v>326</v>
       </c>
       <c r="F33">
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>609</v>
+        <v>410</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>753</v>
+        <v>496</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>26039</v>
+        <v>21729</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" t="s">
         <v>196</v>
       </c>
-      <c r="D34" t="s">
-        <v>340</v>
-      </c>
       <c r="E34" t="s">
-        <v>482</v>
+        <v>282</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G34" t="s">
-        <v>613</v>
+        <v>362</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>757</v>
+        <v>448</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>39306</v>
+        <v>23452</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>226</v>
+        <v>117</v>
       </c>
       <c r="D35" t="s">
-        <v>370</v>
+        <v>203</v>
       </c>
       <c r="E35" t="s">
-        <v>508</v>
+        <v>289</v>
       </c>
       <c r="F35">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G35" t="s">
-        <v>643</v>
+        <v>369</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>787</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>45041</v>
+        <v>35145</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>258</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>402</v>
+        <v>217</v>
       </c>
       <c r="E36" t="s">
-        <v>539</v>
+        <v>301</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G36" t="s">
-        <v>675</v>
+        <v>383</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>819</v>
+        <v>469</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>21729</v>
+        <v>43945</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="C37" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="D37" t="s">
-        <v>319</v>
+        <v>238</v>
       </c>
       <c r="E37" t="s">
-        <v>462</v>
+        <v>320</v>
       </c>
       <c r="F37">
         <v>6.5</v>
       </c>
       <c r="G37" t="s">
-        <v>592</v>
+        <v>404</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>736</v>
+        <v>490</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>23452</v>
+        <v>13749</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>184</v>
+        <v>94</v>
       </c>
       <c r="D38" t="s">
-        <v>328</v>
+        <v>180</v>
       </c>
       <c r="E38" t="s">
-        <v>471</v>
+        <v>266</v>
       </c>
       <c r="F38">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="G38" t="s">
-        <v>601</v>
+        <v>346</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>745</v>
+        <v>432</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>35145</v>
+        <v>19345</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>215</v>
+        <v>102</v>
       </c>
       <c r="D39" t="s">
-        <v>359</v>
+        <v>188</v>
       </c>
       <c r="E39" t="s">
-        <v>499</v>
+        <v>274</v>
       </c>
       <c r="F39">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="G39" t="s">
-        <v>632</v>
+        <v>354</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>776</v>
+        <v>440</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>43945</v>
+        <v>39015</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>242</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>386</v>
+        <v>223</v>
       </c>
       <c r="E40" t="s">
-        <v>523</v>
+        <v>302</v>
       </c>
       <c r="F40">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="G40" t="s">
-        <v>659</v>
+        <v>389</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>803</v>
+        <v>475</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>13749</v>
+        <v>45120</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="C41" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D41" t="s">
-        <v>296</v>
+        <v>248</v>
       </c>
       <c r="E41" t="s">
-        <v>440</v>
+        <v>266</v>
       </c>
       <c r="F41">
         <v>6</v>
       </c>
       <c r="G41" t="s">
-        <v>569</v>
+        <v>414</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>713</v>
+        <v>500</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>19345</v>
+        <v>45427</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>255</v>
       </c>
       <c r="E42" t="s">
-        <v>449</v>
+        <v>335</v>
       </c>
       <c r="F42">
         <v>6</v>
       </c>
       <c r="G42" t="s">
-        <v>578</v>
+        <v>421</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>722</v>
+        <v>507</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>39015</v>
+        <v>45474</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="D43" t="s">
-        <v>369</v>
+        <v>257</v>
       </c>
       <c r="E43" t="s">
-        <v>500</v>
+        <v>337</v>
       </c>
       <c r="F43">
         <v>6</v>
       </c>
       <c r="G43" t="s">
-        <v>642</v>
+        <v>423</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>786</v>
+        <v>509</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>45120</v>
+        <v>45543</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>264</v>
+        <v>173</v>
       </c>
       <c r="D44" t="s">
-        <v>408</v>
+        <v>259</v>
       </c>
       <c r="E44" t="s">
-        <v>440</v>
+        <v>339</v>
       </c>
       <c r="F44">
         <v>6</v>
       </c>
       <c r="G44" t="s">
-        <v>681</v>
+        <v>425</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>825</v>
+        <v>511</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>45427</v>
+        <v>44971</v>
       </c>
       <c r="B45" t="s">
-        <v>132</v>
+        <v>71</v>
       </c>
       <c r="C45" t="s">
-        <v>276</v>
+        <v>157</v>
       </c>
       <c r="D45" t="s">
-        <v>420</v>
+        <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>554</v>
+        <v>325</v>
       </c>
       <c r="F45">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="G45" t="s">
-        <v>693</v>
+        <v>409</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>837</v>
+        <v>495</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>45474</v>
+        <v>36992</v>
       </c>
       <c r="B46" t="s">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="C46" t="s">
-        <v>280</v>
+        <v>134</v>
       </c>
       <c r="D46" t="s">
-        <v>424</v>
+        <v>220</v>
       </c>
       <c r="E46" t="s">
-        <v>558</v>
+        <v>304</v>
       </c>
       <c r="F46">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="G46" t="s">
-        <v>697</v>
+        <v>386</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>841</v>
+        <v>472</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>45543</v>
+        <v>39415</v>
       </c>
       <c r="B47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" t="s">
         <v>139</v>
       </c>
-      <c r="C47" t="s">
-        <v>283</v>
-      </c>
       <c r="D47" t="s">
-        <v>427</v>
+        <v>225</v>
       </c>
       <c r="E47" t="s">
-        <v>560</v>
+        <v>308</v>
       </c>
       <c r="F47">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="G47" t="s">
-        <v>700</v>
+        <v>391</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>844</v>
+        <v>477</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>44971</v>
+        <v>41625</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>254</v>
+        <v>144</v>
       </c>
       <c r="D48" t="s">
-        <v>398</v>
+        <v>230</v>
       </c>
       <c r="E48" t="s">
-        <v>535</v>
+        <v>313</v>
       </c>
       <c r="F48">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="G48" t="s">
-        <v>671</v>
+        <v>396</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>815</v>
+        <v>482</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>36992</v>
+        <v>42319</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>221</v>
+        <v>146</v>
       </c>
       <c r="D49" t="s">
-        <v>365</v>
+        <v>232</v>
       </c>
       <c r="E49" t="s">
-        <v>504</v>
+        <v>315</v>
       </c>
       <c r="F49">
         <v>5.5</v>
       </c>
       <c r="G49" t="s">
-        <v>638</v>
+        <v>398</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>782</v>
+        <v>484</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>39415</v>
+        <v>45133</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C50" t="s">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="D50" t="s">
-        <v>371</v>
+        <v>249</v>
       </c>
       <c r="E50" t="s">
-        <v>509</v>
+        <v>329</v>
       </c>
       <c r="F50">
         <v>5.5</v>
       </c>
       <c r="G50" t="s">
-        <v>644</v>
+        <v>415</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>788</v>
+        <v>501</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>41625</v>
+        <v>45316</v>
       </c>
       <c r="B51" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C51" t="s">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="D51" t="s">
-        <v>376</v>
+        <v>253</v>
       </c>
       <c r="E51" t="s">
-        <v>514</v>
+        <v>333</v>
       </c>
       <c r="F51">
         <v>5.5</v>
       </c>
       <c r="G51" t="s">
-        <v>649</v>
+        <v>419</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>793</v>
+        <v>505</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>42319</v>
+        <v>27862</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="C52" t="s">
-        <v>234</v>
+        <v>127</v>
       </c>
       <c r="D52" t="s">
-        <v>378</v>
+        <v>213</v>
       </c>
       <c r="E52" t="s">
-        <v>516</v>
+        <v>266</v>
       </c>
       <c r="F52">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="G52" t="s">
-        <v>651</v>
+        <v>379</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>795</v>
+        <v>465</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>45133</v>
+        <v>15823</v>
       </c>
       <c r="B53" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>265</v>
+        <v>96</v>
       </c>
       <c r="D53" t="s">
-        <v>409</v>
+        <v>182</v>
       </c>
       <c r="E53" t="s">
-        <v>543</v>
+        <v>268</v>
       </c>
       <c r="F53">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="G53" t="s">
-        <v>682</v>
+        <v>348</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>826</v>
+        <v>434</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>45316</v>
+        <v>38971</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="C54" t="s">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="D54" t="s">
-        <v>416</v>
+        <v>222</v>
       </c>
       <c r="E54" t="s">
-        <v>550</v>
+        <v>306</v>
       </c>
       <c r="F54">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="G54" t="s">
-        <v>689</v>
+        <v>388</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>833</v>
+        <v>474</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>27862</v>
+        <v>40030</v>
       </c>
       <c r="B55" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="D55" t="s">
-        <v>346</v>
+        <v>227</v>
       </c>
       <c r="E55" t="s">
-        <v>440</v>
+        <v>310</v>
       </c>
       <c r="F55">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="G55" t="s">
-        <v>619</v>
+        <v>393</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>763</v>
+        <v>479</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>15823</v>
+        <v>45704</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="D56" t="s">
-        <v>298</v>
+        <v>260</v>
       </c>
       <c r="E56" t="s">
-        <v>442</v>
+        <v>340</v>
       </c>
       <c r="F56">
         <v>5</v>
       </c>
       <c r="G56" t="s">
-        <v>571</v>
+        <v>426</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>715</v>
+        <v>512</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>38971</v>
+        <v>16671</v>
       </c>
       <c r="B57" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>223</v>
+        <v>97</v>
       </c>
       <c r="D57" t="s">
-        <v>367</v>
+        <v>183</v>
       </c>
       <c r="E57" t="s">
-        <v>506</v>
+        <v>269</v>
       </c>
       <c r="F57">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="G57" t="s">
-        <v>640</v>
+        <v>349</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>784</v>
+        <v>435</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>40030</v>
+        <v>29115</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="C58" t="s">
-        <v>229</v>
+        <v>128</v>
       </c>
       <c r="D58" t="s">
-        <v>373</v>
+        <v>214</v>
       </c>
       <c r="E58" t="s">
-        <v>511</v>
+        <v>266</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G58" t="s">
-        <v>646</v>
+        <v>380</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>790</v>
+        <v>466</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>45704</v>
+        <v>40426</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>288</v>
+        <v>143</v>
       </c>
       <c r="D59" t="s">
-        <v>432</v>
+        <v>229</v>
       </c>
       <c r="E59" t="s">
-        <v>563</v>
+        <v>312</v>
       </c>
       <c r="F59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G59" t="s">
-        <v>705</v>
+        <v>395</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>849</v>
+        <v>481</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>22277</v>
+        <v>45048</v>
       </c>
       <c r="B60" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="C60" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>245</v>
       </c>
       <c r="E60" t="s">
-        <v>467</v>
+        <v>327</v>
       </c>
       <c r="F60">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G60" t="s">
-        <v>597</v>
+        <v>411</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>741</v>
+        <v>497</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>16671</v>
+        <v>45049</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="C61" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D61" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="E61" t="s">
-        <v>443</v>
+        <v>302</v>
       </c>
       <c r="F61">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G61" t="s">
-        <v>572</v>
+        <v>412</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>716</v>
+        <v>498</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>29115</v>
+        <v>45240</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="D62" t="s">
-        <v>347</v>
+        <v>250</v>
       </c>
       <c r="E62" t="s">
-        <v>440</v>
+        <v>330</v>
       </c>
       <c r="F62">
         <v>4</v>
       </c>
       <c r="G62" t="s">
-        <v>620</v>
+        <v>416</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>764</v>
+        <v>502</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>40426</v>
+        <v>45871</v>
       </c>
       <c r="B63" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C63" t="s">
-        <v>231</v>
+        <v>177</v>
       </c>
       <c r="D63" t="s">
-        <v>375</v>
+        <v>263</v>
       </c>
       <c r="E63" t="s">
-        <v>513</v>
+        <v>343</v>
       </c>
       <c r="F63">
         <v>4</v>
       </c>
       <c r="G63" t="s">
-        <v>648</v>
+        <v>429</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>792</v>
+        <v>515</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>45048</v>
+        <v>45966</v>
       </c>
       <c r="B64" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>179</v>
       </c>
       <c r="D64" t="s">
-        <v>403</v>
+        <v>265</v>
       </c>
       <c r="E64" t="s">
-        <v>540</v>
+        <v>345</v>
       </c>
       <c r="F64">
         <v>4</v>
       </c>
       <c r="G64" t="s">
-        <v>676</v>
+        <v>431</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>820</v>
+        <v>517</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>45049</v>
+        <v>19157</v>
       </c>
       <c r="B65" t="s">
-        <v>116</v>
+        <v>15</v>
       </c>
       <c r="C65" t="s">
-        <v>260</v>
+        <v>101</v>
       </c>
       <c r="D65" t="s">
-        <v>404</v>
+        <v>187</v>
       </c>
       <c r="E65" t="s">
-        <v>500</v>
+        <v>273</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G65" t="s">
-        <v>677</v>
+        <v>353</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>821</v>
+        <v>439</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>45240</v>
+        <v>19565</v>
       </c>
       <c r="B66" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
-        <v>412</v>
+        <v>190</v>
       </c>
       <c r="E66" t="s">
-        <v>546</v>
+        <v>276</v>
       </c>
       <c r="F66">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G66" t="s">
-        <v>685</v>
+        <v>356</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>829</v>
+        <v>442</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>45871</v>
+        <v>29436</v>
       </c>
       <c r="B67" t="s">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="C67" t="s">
-        <v>292</v>
+        <v>129</v>
       </c>
       <c r="D67" t="s">
-        <v>436</v>
+        <v>215</v>
       </c>
       <c r="E67" t="s">
-        <v>566</v>
+        <v>299</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G67" t="s">
-        <v>709</v>
+        <v>381</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>853</v>
+        <v>467</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>45966</v>
+        <v>34974</v>
       </c>
       <c r="B68" t="s">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="C68" t="s">
-        <v>295</v>
+        <v>130</v>
       </c>
       <c r="D68" t="s">
-        <v>439</v>
+        <v>216</v>
       </c>
       <c r="E68" t="s">
-        <v>568</v>
+        <v>300</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G68" t="s">
-        <v>712</v>
+        <v>382</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>856</v>
+        <v>468</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>19157</v>
+        <v>39451</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D69" t="s">
-        <v>304</v>
+        <v>226</v>
       </c>
       <c r="E69" t="s">
-        <v>448</v>
+        <v>309</v>
       </c>
       <c r="F69">
         <v>3.5</v>
       </c>
       <c r="G69" t="s">
-        <v>577</v>
+        <v>392</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>721</v>
+        <v>478</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>19565</v>
+        <v>43560</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="C70" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D70" t="s">
-        <v>307</v>
+        <v>237</v>
       </c>
       <c r="E70" t="s">
-        <v>451</v>
+        <v>319</v>
       </c>
       <c r="F70">
         <v>3.5</v>
       </c>
       <c r="G70" t="s">
-        <v>580</v>
+        <v>403</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>724</v>
+        <v>489</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>27573</v>
+        <v>45249</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C71" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="D71" t="s">
-        <v>345</v>
+        <v>251</v>
       </c>
       <c r="E71" t="s">
-        <v>487</v>
+        <v>331</v>
       </c>
       <c r="F71">
         <v>3.5</v>
       </c>
       <c r="G71" t="s">
-        <v>618</v>
+        <v>417</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>762</v>
+        <v>503</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>29436</v>
+        <v>45529</v>
       </c>
       <c r="B72" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C72" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D72" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="E72" t="s">
-        <v>488</v>
+        <v>338</v>
       </c>
       <c r="F72">
         <v>3.5</v>
       </c>
       <c r="G72" t="s">
-        <v>621</v>
+        <v>424</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>765</v>
+        <v>510</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>34974</v>
+        <v>45891</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C73" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="D73" t="s">
-        <v>358</v>
+        <v>264</v>
       </c>
       <c r="E73" t="s">
-        <v>498</v>
+        <v>344</v>
       </c>
       <c r="F73">
         <v>3.5</v>
       </c>
       <c r="G73" t="s">
-        <v>631</v>
+        <v>430</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>775</v>
+        <v>516</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>39451</v>
+        <v>21253</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="C74" t="s">
-        <v>228</v>
+        <v>109</v>
       </c>
       <c r="D74" t="s">
-        <v>372</v>
+        <v>195</v>
       </c>
       <c r="E74" t="s">
-        <v>510</v>
+        <v>281</v>
       </c>
       <c r="F74">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G74" t="s">
-        <v>645</v>
+        <v>361</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>789</v>
+        <v>447</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>43560</v>
+        <v>24404</v>
       </c>
       <c r="B75" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
-        <v>241</v>
+        <v>120</v>
       </c>
       <c r="D75" t="s">
-        <v>385</v>
+        <v>206</v>
       </c>
       <c r="E75" t="s">
-        <v>522</v>
+        <v>292</v>
       </c>
       <c r="F75">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G75" t="s">
-        <v>658</v>
+        <v>372</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>802</v>
+        <v>458</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>45249</v>
+        <v>36223</v>
       </c>
       <c r="B76" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="C76" t="s">
-        <v>269</v>
+        <v>133</v>
       </c>
       <c r="D76" t="s">
-        <v>413</v>
+        <v>219</v>
       </c>
       <c r="E76" t="s">
-        <v>547</v>
+        <v>266</v>
       </c>
       <c r="F76">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G76" t="s">
-        <v>686</v>
+        <v>385</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>830</v>
+        <v>471</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>45529</v>
+        <v>44936</v>
       </c>
       <c r="B77" t="s">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="C77" t="s">
-        <v>282</v>
+        <v>156</v>
       </c>
       <c r="D77" t="s">
-        <v>426</v>
+        <v>242</v>
       </c>
       <c r="E77" t="s">
-        <v>559</v>
+        <v>324</v>
       </c>
       <c r="F77">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G77" t="s">
-        <v>699</v>
+        <v>408</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>843</v>
+        <v>494</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>45891</v>
+        <v>17646</v>
       </c>
       <c r="B78" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>294</v>
+        <v>98</v>
       </c>
       <c r="D78" t="s">
-        <v>438</v>
+        <v>184</v>
       </c>
       <c r="E78" t="s">
-        <v>567</v>
+        <v>270</v>
       </c>
       <c r="F78">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G78" t="s">
-        <v>711</v>
+        <v>350</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>855</v>
+        <v>436</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>21253</v>
+        <v>20302</v>
       </c>
       <c r="B79" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C79" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="D79" t="s">
-        <v>314</v>
+        <v>191</v>
       </c>
       <c r="E79" t="s">
-        <v>457</v>
+        <v>277</v>
       </c>
       <c r="F79">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G79" t="s">
-        <v>587</v>
+        <v>357</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>731</v>
+        <v>443</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>24404</v>
+        <v>22263</v>
       </c>
       <c r="B80" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C80" t="s">
-        <v>191</v>
+        <v>113</v>
       </c>
       <c r="D80" t="s">
-        <v>335</v>
+        <v>199</v>
       </c>
       <c r="E80" t="s">
-        <v>478</v>
+        <v>285</v>
       </c>
       <c r="F80">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G80" t="s">
-        <v>608</v>
+        <v>365</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>752</v>
+        <v>451</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>36223</v>
+        <v>22270</v>
       </c>
       <c r="B81" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="C81" t="s">
-        <v>219</v>
+        <v>114</v>
       </c>
       <c r="D81" t="s">
-        <v>363</v>
+        <v>200</v>
       </c>
       <c r="E81" t="s">
-        <v>440</v>
+        <v>286</v>
       </c>
       <c r="F81">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G81" t="s">
-        <v>636</v>
+        <v>366</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>780</v>
+        <v>452</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>44936</v>
+        <v>22518</v>
       </c>
       <c r="B82" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C82" t="s">
-        <v>252</v>
+        <v>115</v>
       </c>
       <c r="D82" t="s">
-        <v>396</v>
+        <v>201</v>
       </c>
       <c r="E82" t="s">
-        <v>533</v>
+        <v>287</v>
       </c>
       <c r="F82">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G82" t="s">
-        <v>669</v>
+        <v>367</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>813</v>
+        <v>453</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>17646</v>
+        <v>27086</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C83" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="D83" t="s">
-        <v>300</v>
+        <v>211</v>
       </c>
       <c r="E83" t="s">
-        <v>444</v>
+        <v>296</v>
       </c>
       <c r="F83">
         <v>3</v>
       </c>
       <c r="G83" t="s">
-        <v>573</v>
+        <v>377</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>717</v>
+        <v>463</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>20302</v>
+        <v>37377</v>
       </c>
       <c r="B84" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C84" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="D84" t="s">
-        <v>308</v>
+        <v>221</v>
       </c>
       <c r="E84" t="s">
-        <v>452</v>
+        <v>305</v>
       </c>
       <c r="F84">
         <v>3</v>
       </c>
       <c r="G84" t="s">
-        <v>581</v>
+        <v>387</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>725</v>
+        <v>473</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>22263</v>
+        <v>43096</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C85" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="D85" t="s">
-        <v>322</v>
+        <v>233</v>
       </c>
       <c r="E85" t="s">
-        <v>465</v>
+        <v>316</v>
       </c>
       <c r="F85">
         <v>3</v>
       </c>
       <c r="G85" t="s">
-        <v>595</v>
+        <v>399</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>739</v>
+        <v>485</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>22270</v>
+        <v>45081</v>
       </c>
       <c r="B86" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C86" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="D86" t="s">
-        <v>323</v>
+        <v>247</v>
       </c>
       <c r="E86" t="s">
-        <v>466</v>
+        <v>328</v>
       </c>
       <c r="F86">
         <v>3</v>
       </c>
       <c r="G86" t="s">
-        <v>596</v>
+        <v>413</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>740</v>
+        <v>499</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>22518</v>
+        <v>45801</v>
       </c>
       <c r="B87" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="C87" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D87" t="s">
-        <v>325</v>
+        <v>262</v>
       </c>
       <c r="E87" t="s">
-        <v>468</v>
+        <v>342</v>
       </c>
       <c r="F87">
         <v>3</v>
       </c>
       <c r="G87" t="s">
-        <v>598</v>
+        <v>428</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>27086</v>
-      </c>
-      <c r="B88" t="s">
-        <v>55</v>
-      </c>
-      <c r="C88" t="s">
-        <v>199</v>
-      </c>
-      <c r="D88" t="s">
-        <v>343</v>
-      </c>
-      <c r="E88" t="s">
-        <v>485</v>
-      </c>
-      <c r="F88">
-        <v>3</v>
-      </c>
-      <c r="G88" t="s">
-        <v>616</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>37377</v>
-      </c>
-      <c r="B89" t="s">
-        <v>78</v>
-      </c>
-      <c r="C89" t="s">
-        <v>222</v>
-      </c>
-      <c r="D89" t="s">
-        <v>366</v>
-      </c>
-      <c r="E89" t="s">
-        <v>505</v>
-      </c>
-      <c r="F89">
-        <v>3</v>
-      </c>
-      <c r="G89" t="s">
-        <v>639</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>43096</v>
-      </c>
-      <c r="B90" t="s">
-        <v>91</v>
-      </c>
-      <c r="C90" t="s">
-        <v>235</v>
-      </c>
-      <c r="D90" t="s">
-        <v>379</v>
-      </c>
-      <c r="E90" t="s">
-        <v>517</v>
-      </c>
-      <c r="F90">
-        <v>3</v>
-      </c>
-      <c r="G90" t="s">
-        <v>652</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>45081</v>
-      </c>
-      <c r="B91" t="s">
-        <v>119</v>
-      </c>
-      <c r="C91" t="s">
-        <v>263</v>
-      </c>
-      <c r="D91" t="s">
-        <v>407</v>
-      </c>
-      <c r="E91" t="s">
-        <v>542</v>
-      </c>
-      <c r="F91">
-        <v>3</v>
-      </c>
-      <c r="G91" t="s">
-        <v>680</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>45801</v>
-      </c>
-      <c r="B92" t="s">
-        <v>147</v>
-      </c>
-      <c r="C92" t="s">
-        <v>291</v>
-      </c>
-      <c r="D92" t="s">
-        <v>435</v>
-      </c>
-      <c r="E92" t="s">
-        <v>565</v>
-      </c>
-      <c r="F92">
-        <v>3</v>
-      </c>
-      <c r="G92" t="s">
-        <v>708</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>45148</v>
-      </c>
-      <c r="B93" t="s">
-        <v>122</v>
-      </c>
-      <c r="C93" t="s">
-        <v>266</v>
-      </c>
-      <c r="D93" t="s">
-        <v>410</v>
-      </c>
-      <c r="E93" t="s">
-        <v>544</v>
-      </c>
-      <c r="F93">
-        <v>2.8</v>
-      </c>
-      <c r="G93" t="s">
-        <v>683</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>30898</v>
-      </c>
-      <c r="B94" t="s">
-        <v>67</v>
-      </c>
-      <c r="C94" t="s">
-        <v>211</v>
-      </c>
-      <c r="D94" t="s">
-        <v>355</v>
-      </c>
-      <c r="E94" t="s">
-        <v>495</v>
-      </c>
-      <c r="F94">
-        <v>2.7</v>
-      </c>
-      <c r="G94" t="s">
-        <v>628</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>44751</v>
-      </c>
-      <c r="B95" t="s">
-        <v>105</v>
-      </c>
-      <c r="C95" t="s">
-        <v>249</v>
-      </c>
-      <c r="D95" t="s">
-        <v>393</v>
-      </c>
-      <c r="E95" t="s">
-        <v>530</v>
-      </c>
-      <c r="F95">
-        <v>2.7</v>
-      </c>
-      <c r="G95" t="s">
-        <v>666</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>21481</v>
-      </c>
-      <c r="B96" t="s">
-        <v>28</v>
-      </c>
-      <c r="C96" t="s">
-        <v>172</v>
-      </c>
-      <c r="D96" t="s">
-        <v>316</v>
-      </c>
-      <c r="E96" t="s">
-        <v>459</v>
-      </c>
-      <c r="F96">
-        <v>2.5</v>
-      </c>
-      <c r="G96" t="s">
-        <v>589</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>23780</v>
-      </c>
-      <c r="B97" t="s">
-        <v>43</v>
-      </c>
-      <c r="C97" t="s">
-        <v>187</v>
-      </c>
-      <c r="D97" t="s">
-        <v>331</v>
-      </c>
-      <c r="E97" t="s">
-        <v>474</v>
-      </c>
-      <c r="F97">
-        <v>2.5</v>
-      </c>
-      <c r="G97" t="s">
-        <v>604</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>23887</v>
-      </c>
-      <c r="B98" t="s">
-        <v>44</v>
-      </c>
-      <c r="C98" t="s">
-        <v>188</v>
-      </c>
-      <c r="D98" t="s">
-        <v>332</v>
-      </c>
-      <c r="E98" t="s">
-        <v>475</v>
-      </c>
-      <c r="F98">
-        <v>2.5</v>
-      </c>
-      <c r="G98" t="s">
-        <v>605</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>24009</v>
-      </c>
-      <c r="B99" t="s">
-        <v>45</v>
-      </c>
-      <c r="C99" t="s">
-        <v>189</v>
-      </c>
-      <c r="D99" t="s">
-        <v>333</v>
-      </c>
-      <c r="E99" t="s">
-        <v>476</v>
-      </c>
-      <c r="F99">
-        <v>2.5</v>
-      </c>
-      <c r="G99" t="s">
-        <v>606</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>39007</v>
-      </c>
-      <c r="B100" t="s">
-        <v>80</v>
-      </c>
-      <c r="C100" t="s">
-        <v>224</v>
-      </c>
-      <c r="D100" t="s">
-        <v>368</v>
-      </c>
-      <c r="E100" t="s">
-        <v>507</v>
-      </c>
-      <c r="F100">
-        <v>2.5</v>
-      </c>
-      <c r="G100" t="s">
-        <v>641</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>43543</v>
-      </c>
-      <c r="B101" t="s">
-        <v>96</v>
-      </c>
-      <c r="C101" t="s">
-        <v>240</v>
-      </c>
-      <c r="D101" t="s">
-        <v>384</v>
-      </c>
-      <c r="E101" t="s">
-        <v>521</v>
-      </c>
-      <c r="F101">
-        <v>2.5</v>
-      </c>
-      <c r="G101" t="s">
-        <v>657</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>44734</v>
-      </c>
-      <c r="B102" t="s">
-        <v>103</v>
-      </c>
-      <c r="C102" t="s">
-        <v>247</v>
-      </c>
-      <c r="D102" t="s">
-        <v>391</v>
-      </c>
-      <c r="E102" t="s">
-        <v>528</v>
-      </c>
-      <c r="F102">
-        <v>2.5</v>
-      </c>
-      <c r="G102" t="s">
-        <v>664</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>45387</v>
-      </c>
-      <c r="B103" t="s">
-        <v>129</v>
-      </c>
-      <c r="C103" t="s">
-        <v>273</v>
-      </c>
-      <c r="D103" t="s">
-        <v>417</v>
-      </c>
-      <c r="E103" t="s">
-        <v>551</v>
-      </c>
-      <c r="F103">
-        <v>2.5</v>
-      </c>
-      <c r="G103" t="s">
-        <v>690</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>45470</v>
-      </c>
-      <c r="B104" t="s">
-        <v>134</v>
-      </c>
-      <c r="C104" t="s">
-        <v>278</v>
-      </c>
-      <c r="D104" t="s">
-        <v>422</v>
-      </c>
-      <c r="E104" t="s">
-        <v>556</v>
-      </c>
-      <c r="F104">
-        <v>2.5</v>
-      </c>
-      <c r="G104" t="s">
-        <v>695</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>21495</v>
-      </c>
-      <c r="B105" t="s">
-        <v>29</v>
-      </c>
-      <c r="C105" t="s">
-        <v>173</v>
-      </c>
-      <c r="D105" t="s">
-        <v>317</v>
-      </c>
-      <c r="E105" t="s">
-        <v>460</v>
-      </c>
-      <c r="F105">
-        <v>2.25</v>
-      </c>
-      <c r="G105" t="s">
-        <v>590</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>45602</v>
-      </c>
-      <c r="B106" t="s">
-        <v>141</v>
-      </c>
-      <c r="C106" t="s">
-        <v>285</v>
-      </c>
-      <c r="D106" t="s">
-        <v>429</v>
-      </c>
-      <c r="E106" t="s">
-        <v>544</v>
-      </c>
-      <c r="F106">
-        <v>2.1</v>
-      </c>
-      <c r="G106" t="s">
-        <v>702</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>20425</v>
-      </c>
-      <c r="B107" t="s">
-        <v>21</v>
-      </c>
-      <c r="C107" t="s">
-        <v>165</v>
-      </c>
-      <c r="D107" t="s">
-        <v>309</v>
-      </c>
-      <c r="E107" t="s">
-        <v>453</v>
-      </c>
-      <c r="F107">
-        <v>2</v>
-      </c>
-      <c r="G107" t="s">
-        <v>582</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>21470</v>
-      </c>
-      <c r="B108" t="s">
-        <v>27</v>
-      </c>
-      <c r="C108" t="s">
-        <v>171</v>
-      </c>
-      <c r="D108" t="s">
-        <v>315</v>
-      </c>
-      <c r="E108" t="s">
-        <v>458</v>
-      </c>
-      <c r="F108">
-        <v>2</v>
-      </c>
-      <c r="G108" t="s">
-        <v>588</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>29808</v>
-      </c>
-      <c r="B109" t="s">
-        <v>63</v>
-      </c>
-      <c r="C109" t="s">
-        <v>207</v>
-      </c>
-      <c r="D109" t="s">
-        <v>351</v>
-      </c>
-      <c r="E109" t="s">
-        <v>491</v>
-      </c>
-      <c r="F109">
-        <v>2</v>
-      </c>
-      <c r="G109" t="s">
-        <v>624</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>30517</v>
-      </c>
-      <c r="B110" t="s">
-        <v>65</v>
-      </c>
-      <c r="C110" t="s">
-        <v>209</v>
-      </c>
-      <c r="D110" t="s">
-        <v>353</v>
-      </c>
-      <c r="E110" t="s">
-        <v>493</v>
-      </c>
-      <c r="F110">
-        <v>2</v>
-      </c>
-      <c r="G110" t="s">
-        <v>626</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>30862</v>
-      </c>
-      <c r="B111" t="s">
-        <v>66</v>
-      </c>
-      <c r="C111" t="s">
-        <v>210</v>
-      </c>
-      <c r="D111" t="s">
-        <v>354</v>
-      </c>
-      <c r="E111" t="s">
-        <v>494</v>
-      </c>
-      <c r="F111">
-        <v>2</v>
-      </c>
-      <c r="G111" t="s">
-        <v>627</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>32216</v>
-      </c>
-      <c r="B112" t="s">
-        <v>68</v>
-      </c>
-      <c r="C112" t="s">
-        <v>212</v>
-      </c>
-      <c r="D112" t="s">
-        <v>356</v>
-      </c>
-      <c r="E112" t="s">
-        <v>496</v>
-      </c>
-      <c r="F112">
-        <v>2</v>
-      </c>
-      <c r="G112" t="s">
-        <v>629</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>43519</v>
-      </c>
-      <c r="B113" t="s">
-        <v>95</v>
-      </c>
-      <c r="C113" t="s">
-        <v>239</v>
-      </c>
-      <c r="D113" t="s">
-        <v>383</v>
-      </c>
-      <c r="E113" t="s">
-        <v>520</v>
-      </c>
-      <c r="F113">
-        <v>2</v>
-      </c>
-      <c r="G113" t="s">
-        <v>656</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>44394</v>
-      </c>
-      <c r="B114" t="s">
-        <v>100</v>
-      </c>
-      <c r="C114" t="s">
-        <v>244</v>
-      </c>
-      <c r="D114" t="s">
-        <v>388</v>
-      </c>
-      <c r="E114" t="s">
-        <v>525</v>
-      </c>
-      <c r="F114">
-        <v>2</v>
-      </c>
-      <c r="G114" t="s">
-        <v>661</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <v>44638</v>
-      </c>
-      <c r="B115" t="s">
-        <v>102</v>
-      </c>
-      <c r="C115" t="s">
-        <v>246</v>
-      </c>
-      <c r="D115" t="s">
-        <v>390</v>
-      </c>
-      <c r="E115" t="s">
-        <v>527</v>
-      </c>
-      <c r="F115">
-        <v>2</v>
-      </c>
-      <c r="G115" t="s">
-        <v>663</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <v>45065</v>
-      </c>
-      <c r="B116" t="s">
-        <v>118</v>
-      </c>
-      <c r="C116" t="s">
-        <v>262</v>
-      </c>
-      <c r="D116" t="s">
-        <v>406</v>
-      </c>
-      <c r="E116" t="s">
-        <v>541</v>
-      </c>
-      <c r="F116">
-        <v>2</v>
-      </c>
-      <c r="G116" t="s">
-        <v>679</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>45500</v>
-      </c>
-      <c r="B117" t="s">
-        <v>137</v>
-      </c>
-      <c r="C117" t="s">
-        <v>281</v>
-      </c>
-      <c r="D117" t="s">
-        <v>425</v>
-      </c>
-      <c r="E117" t="s">
-        <v>500</v>
-      </c>
-      <c r="F117">
-        <v>2</v>
-      </c>
-      <c r="G117" t="s">
-        <v>698</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <v>45620</v>
-      </c>
-      <c r="B118" t="s">
-        <v>142</v>
-      </c>
-      <c r="C118" t="s">
-        <v>286</v>
-      </c>
-      <c r="D118" t="s">
-        <v>430</v>
-      </c>
-      <c r="E118" t="s">
-        <v>562</v>
-      </c>
-      <c r="F118">
-        <v>2</v>
-      </c>
-      <c r="G118" t="s">
-        <v>703</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <v>29790</v>
-      </c>
-      <c r="B119" t="s">
-        <v>61</v>
-      </c>
-      <c r="C119" t="s">
-        <v>205</v>
-      </c>
-      <c r="D119" t="s">
-        <v>349</v>
-      </c>
-      <c r="E119" t="s">
-        <v>489</v>
-      </c>
-      <c r="F119">
-        <v>1.8</v>
-      </c>
-      <c r="G119" t="s">
-        <v>622</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120">
-        <v>36029</v>
-      </c>
-      <c r="B120" t="s">
-        <v>72</v>
-      </c>
-      <c r="C120" t="s">
-        <v>216</v>
-      </c>
-      <c r="D120" t="s">
-        <v>360</v>
-      </c>
-      <c r="E120" t="s">
-        <v>500</v>
-      </c>
-      <c r="F120">
-        <v>1.8</v>
-      </c>
-      <c r="G120" t="s">
-        <v>633</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <v>44957</v>
-      </c>
-      <c r="B121" t="s">
-        <v>109</v>
-      </c>
-      <c r="C121" t="s">
-        <v>253</v>
-      </c>
-      <c r="D121" t="s">
-        <v>397</v>
-      </c>
-      <c r="E121" t="s">
-        <v>534</v>
-      </c>
-      <c r="F121">
-        <v>1.75</v>
-      </c>
-      <c r="G121" t="s">
-        <v>670</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <v>29794</v>
-      </c>
-      <c r="B122" t="s">
-        <v>62</v>
-      </c>
-      <c r="C122" t="s">
-        <v>206</v>
-      </c>
-      <c r="D122" t="s">
-        <v>350</v>
-      </c>
-      <c r="E122" t="s">
-        <v>490</v>
-      </c>
-      <c r="F122">
-        <v>1.5</v>
-      </c>
-      <c r="G122" t="s">
-        <v>623</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <v>45003</v>
-      </c>
-      <c r="B123" t="s">
-        <v>112</v>
-      </c>
-      <c r="C123" t="s">
-        <v>256</v>
-      </c>
-      <c r="D123" t="s">
-        <v>400</v>
-      </c>
-      <c r="E123" t="s">
-        <v>537</v>
-      </c>
-      <c r="F123">
-        <v>1.5</v>
-      </c>
-      <c r="G123" t="s">
-        <v>673</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>45055</v>
-      </c>
-      <c r="B124" t="s">
-        <v>117</v>
-      </c>
-      <c r="C124" t="s">
-        <v>261</v>
-      </c>
-      <c r="D124" t="s">
-        <v>405</v>
-      </c>
-      <c r="E124" t="s">
-        <v>541</v>
-      </c>
-      <c r="F124">
-        <v>1.5</v>
-      </c>
-      <c r="G124" t="s">
-        <v>678</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>45396</v>
-      </c>
-      <c r="B125" t="s">
-        <v>130</v>
-      </c>
-      <c r="C125" t="s">
-        <v>274</v>
-      </c>
-      <c r="D125" t="s">
-        <v>418</v>
-      </c>
-      <c r="E125" t="s">
-        <v>552</v>
-      </c>
-      <c r="F125">
-        <v>1.5</v>
-      </c>
-      <c r="G125" t="s">
-        <v>691</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <v>26407</v>
-      </c>
-      <c r="B126" t="s">
-        <v>54</v>
-      </c>
-      <c r="C126" t="s">
-        <v>198</v>
-      </c>
-      <c r="D126" t="s">
-        <v>342</v>
-      </c>
-      <c r="E126" t="s">
-        <v>484</v>
-      </c>
-      <c r="F126">
-        <v>1.3</v>
-      </c>
-      <c r="G126" t="s">
-        <v>615</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <v>45878</v>
-      </c>
-      <c r="B127" t="s">
-        <v>149</v>
-      </c>
-      <c r="C127" t="s">
-        <v>293</v>
-      </c>
-      <c r="D127" t="s">
-        <v>437</v>
-      </c>
-      <c r="E127" t="s">
-        <v>460</v>
-      </c>
-      <c r="F127">
-        <v>1.25</v>
-      </c>
-      <c r="G127" t="s">
-        <v>710</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <v>21189</v>
-      </c>
-      <c r="B128" t="s">
-        <v>25</v>
-      </c>
-      <c r="C128" t="s">
-        <v>169</v>
-      </c>
-      <c r="D128" t="s">
-        <v>313</v>
-      </c>
-      <c r="E128" t="s">
-        <v>440</v>
-      </c>
-      <c r="F128">
-        <v>1</v>
-      </c>
-      <c r="G128" t="s">
-        <v>586</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <v>24371</v>
-      </c>
-      <c r="B129" t="s">
-        <v>46</v>
-      </c>
-      <c r="C129" t="s">
-        <v>190</v>
-      </c>
-      <c r="D129" t="s">
-        <v>334</v>
-      </c>
-      <c r="E129" t="s">
-        <v>477</v>
-      </c>
-      <c r="F129">
-        <v>1</v>
-      </c>
-      <c r="G129" t="s">
-        <v>607</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130">
-        <v>25426</v>
-      </c>
-      <c r="B130" t="s">
-        <v>51</v>
-      </c>
-      <c r="C130" t="s">
-        <v>195</v>
-      </c>
-      <c r="D130" t="s">
-        <v>339</v>
-      </c>
-      <c r="E130" t="s">
-        <v>481</v>
-      </c>
-      <c r="F130">
-        <v>1</v>
-      </c>
-      <c r="G130" t="s">
-        <v>612</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <v>26262</v>
-      </c>
-      <c r="B131" t="s">
-        <v>53</v>
-      </c>
-      <c r="C131" t="s">
-        <v>197</v>
-      </c>
-      <c r="D131" t="s">
-        <v>341</v>
-      </c>
-      <c r="E131" t="s">
-        <v>483</v>
-      </c>
-      <c r="F131">
-        <v>1</v>
-      </c>
-      <c r="G131" t="s">
-        <v>614</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <v>33209</v>
-      </c>
-      <c r="B132" t="s">
-        <v>69</v>
-      </c>
-      <c r="C132" t="s">
-        <v>213</v>
-      </c>
-      <c r="D132" t="s">
-        <v>357</v>
-      </c>
-      <c r="E132" t="s">
-        <v>497</v>
-      </c>
-      <c r="F132">
-        <v>1</v>
-      </c>
-      <c r="G132" t="s">
-        <v>630</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <v>36631</v>
-      </c>
-      <c r="B133" t="s">
-        <v>76</v>
-      </c>
-      <c r="C133" t="s">
-        <v>220</v>
-      </c>
-      <c r="D133" t="s">
-        <v>364</v>
-      </c>
-      <c r="E133" t="s">
-        <v>503</v>
-      </c>
-      <c r="F133">
-        <v>1</v>
-      </c>
-      <c r="G133" t="s">
-        <v>637</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134">
-        <v>45008</v>
-      </c>
-      <c r="B134" t="s">
-        <v>113</v>
-      </c>
-      <c r="C134" t="s">
-        <v>257</v>
-      </c>
-      <c r="D134" t="s">
-        <v>401</v>
-      </c>
-      <c r="E134" t="s">
-        <v>538</v>
-      </c>
-      <c r="F134">
-        <v>1</v>
-      </c>
-      <c r="G134" t="s">
-        <v>674</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <v>45584</v>
-      </c>
-      <c r="B135" t="s">
-        <v>140</v>
-      </c>
-      <c r="C135" t="s">
-        <v>284</v>
-      </c>
-      <c r="D135" t="s">
-        <v>428</v>
-      </c>
-      <c r="E135" t="s">
-        <v>561</v>
-      </c>
-      <c r="F135">
-        <v>1</v>
-      </c>
-      <c r="G135" t="s">
-        <v>701</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>36124</v>
-      </c>
-      <c r="B136" t="s">
-        <v>73</v>
-      </c>
-      <c r="C136" t="s">
-        <v>217</v>
-      </c>
-      <c r="D136" t="s">
-        <v>361</v>
-      </c>
-      <c r="E136" t="s">
-        <v>501</v>
-      </c>
-      <c r="F136">
-        <v>0.7</v>
-      </c>
-      <c r="G136" t="s">
-        <v>634</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>44816</v>
-      </c>
-      <c r="B137" t="s">
-        <v>107</v>
-      </c>
-      <c r="C137" t="s">
-        <v>251</v>
-      </c>
-      <c r="D137" t="s">
-        <v>395</v>
-      </c>
-      <c r="E137" t="s">
-        <v>532</v>
-      </c>
-      <c r="F137">
-        <v>0.7</v>
-      </c>
-      <c r="G137" t="s">
-        <v>668</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <v>29954</v>
-      </c>
-      <c r="B138" t="s">
-        <v>64</v>
-      </c>
-      <c r="C138" t="s">
-        <v>208</v>
-      </c>
-      <c r="D138" t="s">
-        <v>352</v>
-      </c>
-      <c r="E138" t="s">
-        <v>492</v>
-      </c>
-      <c r="F138">
-        <v>0.6</v>
-      </c>
-      <c r="G138" t="s">
-        <v>625</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139">
-        <v>44760</v>
-      </c>
-      <c r="B139" t="s">
-        <v>106</v>
-      </c>
-      <c r="C139" t="s">
-        <v>250</v>
-      </c>
-      <c r="D139" t="s">
-        <v>394</v>
-      </c>
-      <c r="E139" t="s">
-        <v>531</v>
-      </c>
-      <c r="F139">
-        <v>0.5</v>
-      </c>
-      <c r="G139" t="s">
-        <v>667</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140">
-        <v>45219</v>
-      </c>
-      <c r="B140" t="s">
-        <v>123</v>
-      </c>
-      <c r="C140" t="s">
-        <v>267</v>
-      </c>
-      <c r="D140" t="s">
-        <v>411</v>
-      </c>
-      <c r="E140" t="s">
-        <v>545</v>
-      </c>
-      <c r="F140">
-        <v>0.5</v>
-      </c>
-      <c r="G140" t="s">
-        <v>684</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141">
-        <v>45684</v>
-      </c>
-      <c r="B141" t="s">
-        <v>143</v>
-      </c>
-      <c r="C141" t="s">
-        <v>287</v>
-      </c>
-      <c r="D141" t="s">
-        <v>431</v>
-      </c>
-      <c r="E141" t="s">
-        <v>562</v>
-      </c>
-      <c r="F141">
-        <v>0.5</v>
-      </c>
-      <c r="G141" t="s">
-        <v>704</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142">
-        <v>44994</v>
-      </c>
-      <c r="B142" t="s">
-        <v>111</v>
-      </c>
-      <c r="C142" t="s">
-        <v>255</v>
-      </c>
-      <c r="D142" t="s">
-        <v>399</v>
-      </c>
-      <c r="E142" t="s">
-        <v>536</v>
-      </c>
-      <c r="F142">
-        <v>0.4</v>
-      </c>
-      <c r="G142" t="s">
-        <v>672</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143">
-        <v>45273</v>
-      </c>
-      <c r="B143" t="s">
-        <v>126</v>
-      </c>
-      <c r="C143" t="s">
-        <v>270</v>
-      </c>
-      <c r="D143" t="s">
-        <v>414</v>
-      </c>
-      <c r="E143" t="s">
-        <v>548</v>
-      </c>
-      <c r="F143">
-        <v>0</v>
-      </c>
-      <c r="G143" t="s">
-        <v>687</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144">
-        <v>45472</v>
-      </c>
-      <c r="B144" t="s">
-        <v>135</v>
-      </c>
-      <c r="C144" t="s">
-        <v>279</v>
-      </c>
-      <c r="D144" t="s">
-        <v>423</v>
-      </c>
-      <c r="E144" t="s">
-        <v>557</v>
-      </c>
-      <c r="F144">
-        <v>0</v>
-      </c>
-      <c r="G144" t="s">
-        <v>696</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145">
-        <v>45757</v>
-      </c>
-      <c r="B145" t="s">
-        <v>146</v>
-      </c>
-      <c r="C145" t="s">
-        <v>290</v>
-      </c>
-      <c r="D145" t="s">
-        <v>434</v>
-      </c>
-      <c r="E145" t="s">
-        <v>440</v>
-      </c>
-      <c r="F145">
-        <v>0</v>
-      </c>
-      <c r="G145" t="s">
-        <v>707</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>851</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H145" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H145">
-      <sortCondition descending="1" ref="F1:F145"/>
+  <autoFilter ref="A1:H87" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H87">
+      <sortCondition sortBy="cellColor" ref="C1:C87" dxfId="4"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="H41" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="H19" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="H56" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="H61" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H83" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="H3" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="H15" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H20" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="H69" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="H42" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="H6" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="H70" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="H84" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="H107" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="H7" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="H11" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="H8" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="H128" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="H79" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="H108" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="H96" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="H105" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="H12" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="H37" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="H31" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="H13" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="H85" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="H86" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="H60" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="H87" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="H27" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="H28" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="H38" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="H16" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="H32" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="H97" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="H98" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="H99" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="H129" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="H80" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="H33" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="H21" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="H17" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="H130" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="H34" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="H131" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="H126" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="H88" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="H22" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="H71" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="H55" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="H62" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="H72" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="H119" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="H122" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="H109" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="H138" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="H110" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="H111" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="H94" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="H112" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="H132" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="H73" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="H39" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="H120" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="H136" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="H4" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="H81" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="H133" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="H49" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="H89" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="H57" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="H100" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="H43" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="H35" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="H50" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="H74" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="H58" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="H9" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="H63" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="H51" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="H23" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="H52" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="H90" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="H14" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="H26" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="H24" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="H113" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="H101" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="H75" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="H40" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="H2" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="H114" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="H29" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="H115" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="H102" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="H18" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="H95" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="H139" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="H137" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="H82" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="H121" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="H48" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="H142" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="H123" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="H134" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="H36" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="H64" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="H65" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="H124" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="H116" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="H91" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="H44" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="H53" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="H93" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="H140" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="H66" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="H76" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="H143" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="H30" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="H54" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="H103" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="H125" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="H10" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="H45" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="H25" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="H104" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="H144" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="H46" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="H117" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="H77" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="H47" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="H135" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="H106" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="H118" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="H141" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="H59" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="H5" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="H145" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="H92" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="H67" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="H127" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="H78" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="H68" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="H38" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H17" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="H53" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="H57" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="H78" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="H13" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="H18" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="H65" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="H39" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="H5" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="H66" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="H79" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="H6" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="H10" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="H7" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="H74" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="H34" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="H28" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="H11" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="H80" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="H81" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="H82" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="H25" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="H35" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="H14" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="H29" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="H75" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="H30" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="H19" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="H15" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="H31" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="H83" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="H20" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="H52" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="H58" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="H67" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="H68" r:id="rId37" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="H36" r:id="rId38" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="H3" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="H76" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="H46" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="H84" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="H54" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="H40" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="H32" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="H47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="H69" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="H55" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="H8" r:id="rId49" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="H59" r:id="rId50" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="H48" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="H21" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="H49" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="H85" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="H12" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="H24" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="H22" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="H70" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="H37" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="H2" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="H26" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="H16" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="H77" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="H45" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="H33" r:id="rId65" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="H60" r:id="rId66" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="H61" r:id="rId67" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="H86" r:id="rId68" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="H41" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="H50" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="H62" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="H71" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="H27" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="H51" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="H9" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="H42" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="H23" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="H43" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="H72" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="H44" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="H56" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="H4" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="H87" r:id="rId83" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="H63" r:id="rId84" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="H73" r:id="rId85" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="H64" r:id="rId86" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
